--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/дв 29,06,26 лгрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/дв 29,06,26 лгрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\29,06,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930180E1-BB24-4433-A008-3B74CC2F2F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE48D93-5991-454E-BA9C-8F88CF05FBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -894,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA499"/>
+  <dimension ref="A1:AZ499"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -915,10 +915,10 @@
     <col min="24" max="28" width="6" customWidth="1"/>
     <col min="29" max="29" width="28" customWidth="1"/>
     <col min="30" max="31" width="7" customWidth="1"/>
-    <col min="32" max="53" width="8" customWidth="1"/>
+    <col min="32" max="52" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -971,9 +971,8 @@
       <c r="AX1" s="1"/>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
-      <c r="BA1" s="1"/>
-    </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1026,9 +1025,8 @@
       <c r="AX2" s="1"/>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
-      <c r="BA2" s="1"/>
-    </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1143,9 +1141,8 @@
       <c r="AX3" s="1"/>
       <c r="AY3" s="1"/>
       <c r="AZ3" s="1"/>
-      <c r="BA3" s="1"/>
-    </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1220,9 +1217,8 @@
       <c r="AX4" s="1"/>
       <c r="AY4" s="1"/>
       <c r="AZ4" s="1"/>
-      <c r="BA4" s="1"/>
-    </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1311,11 +1307,11 @@
         <f>SUM(AE6:AE499)</f>
         <v>4134.92</v>
       </c>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="4">
-        <f>SUM(AG6:AG499)</f>
+      <c r="AF5" s="4">
+        <f>SUM(AF6:AF499)</f>
         <v>1478.2237999999998</v>
       </c>
+      <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
@@ -1335,9 +1331,8 @@
       <c r="AX5" s="1"/>
       <c r="AY5" s="1"/>
       <c r="AZ5" s="1"/>
-      <c r="BA5" s="1"/>
-    </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -1424,11 +1419,11 @@
         <f>G6*S6</f>
         <v>0</v>
       </c>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="1">
+      <c r="AF6" s="1">
         <f>P6*G6</f>
         <v>9.9200000000000017</v>
       </c>
+      <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
@@ -1448,9 +1443,8 @@
       <c r="AX6" s="1"/>
       <c r="AY6" s="1"/>
       <c r="AZ6" s="1"/>
-      <c r="BA6" s="1"/>
-    </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
@@ -1533,11 +1527,11 @@
         <f t="shared" ref="AE7:AE70" si="8">G7*S7</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="1">
-        <f t="shared" ref="AG7:AG70" si="9">P7*G7</f>
+      <c r="AF7" s="1">
+        <f t="shared" ref="AF7:AF70" si="9">P7*G7</f>
         <v>0.86699999999999999</v>
       </c>
+      <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
@@ -1557,9 +1551,8 @@
       <c r="AX7" s="1"/>
       <c r="AY7" s="1"/>
       <c r="AZ7" s="1"/>
-      <c r="BA7" s="1"/>
-    </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1647,11 +1640,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1">
+      <c r="AF8" s="1">
         <f t="shared" si="9"/>
         <v>2.85</v>
       </c>
+      <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -1671,9 +1664,8 @@
       <c r="AX8" s="1"/>
       <c r="AY8" s="1"/>
       <c r="AZ8" s="1"/>
-      <c r="BA8" s="1"/>
-    </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -1711,7 +1703,7 @@
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="1">
+      <c r="O9" s="14">
         <v>700</v>
       </c>
       <c r="P9" s="1">
@@ -1764,11 +1756,11 @@
         <f t="shared" si="8"/>
         <v>675</v>
       </c>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1">
+      <c r="AF9" s="1">
         <f t="shared" si="9"/>
         <v>158.0384</v>
       </c>
+      <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -1788,9 +1780,8 @@
       <c r="AX9" s="1"/>
       <c r="AY9" s="1"/>
       <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-    </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1873,11 +1864,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1">
+      <c r="AF10" s="1">
         <f t="shared" si="9"/>
         <v>5.0554000000000006</v>
       </c>
+      <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
@@ -1897,9 +1888,8 @@
       <c r="AX10" s="1"/>
       <c r="AY10" s="1"/>
       <c r="AZ10" s="1"/>
-      <c r="BA10" s="1"/>
-    </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -1937,7 +1927,7 @@
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="1">
+      <c r="O11" s="14">
         <v>350</v>
       </c>
       <c r="P11" s="1">
@@ -1990,11 +1980,11 @@
         <f t="shared" si="8"/>
         <v>113</v>
       </c>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1">
+      <c r="AF11" s="1">
         <f t="shared" si="9"/>
         <v>41.221199999999996</v>
       </c>
+      <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
@@ -2014,9 +2004,8 @@
       <c r="AX11" s="1"/>
       <c r="AY11" s="1"/>
       <c r="AZ11" s="1"/>
-      <c r="BA11" s="1"/>
-    </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
@@ -2054,7 +2043,7 @@
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="1">
+      <c r="O12" s="14">
         <v>560</v>
       </c>
       <c r="P12" s="1">
@@ -2107,11 +2096,11 @@
         <f t="shared" si="8"/>
         <v>167</v>
       </c>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1">
+      <c r="AF12" s="1">
         <f t="shared" si="9"/>
         <v>67.460999999999999</v>
       </c>
+      <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
@@ -2131,9 +2120,8 @@
       <c r="AX12" s="1"/>
       <c r="AY12" s="1"/>
       <c r="AZ12" s="1"/>
-      <c r="BA12" s="1"/>
-    </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
@@ -2219,11 +2207,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF13" s="1"/>
-      <c r="AG13" s="1">
+      <c r="AF13" s="1">
         <f t="shared" si="9"/>
         <v>3.95</v>
       </c>
+      <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
@@ -2243,9 +2231,8 @@
       <c r="AX13" s="1"/>
       <c r="AY13" s="1"/>
       <c r="AZ13" s="1"/>
-      <c r="BA13" s="1"/>
-    </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>41</v>
       </c>
@@ -2333,11 +2320,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1">
+      <c r="AF14" s="1">
         <f t="shared" si="9"/>
         <v>16.722799999999999</v>
       </c>
+      <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
@@ -2357,9 +2344,8 @@
       <c r="AX14" s="1"/>
       <c r="AY14" s="1"/>
       <c r="AZ14" s="1"/>
-      <c r="BA14" s="1"/>
-    </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -2444,11 +2430,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF15" s="1"/>
-      <c r="AG15" s="1">
+      <c r="AF15" s="1">
         <f t="shared" si="9"/>
         <v>3.85</v>
       </c>
+      <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2468,9 +2454,8 @@
       <c r="AX15" s="1"/>
       <c r="AY15" s="1"/>
       <c r="AZ15" s="1"/>
-      <c r="BA15" s="1"/>
-    </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
@@ -2556,11 +2541,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1">
+      <c r="AF16" s="1">
         <f t="shared" si="9"/>
         <v>11.36</v>
       </c>
+      <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
@@ -2580,9 +2565,8 @@
       <c r="AX16" s="1"/>
       <c r="AY16" s="1"/>
       <c r="AZ16" s="1"/>
-      <c r="BA16" s="1"/>
-    </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -2673,11 +2657,11 @@
         <f t="shared" si="8"/>
         <v>67</v>
       </c>
-      <c r="AF17" s="1"/>
-      <c r="AG17" s="1">
+      <c r="AF17" s="1">
         <f t="shared" si="9"/>
         <v>51.934000000000005</v>
       </c>
+      <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
@@ -2697,9 +2681,8 @@
       <c r="AX17" s="1"/>
       <c r="AY17" s="1"/>
       <c r="AZ17" s="1"/>
-      <c r="BA17" s="1"/>
-    </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>45</v>
       </c>
@@ -2782,11 +2765,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF18" s="1"/>
-      <c r="AG18" s="1">
+      <c r="AF18" s="1">
         <f t="shared" si="9"/>
         <v>6.0518000000000001</v>
       </c>
+      <c r="AG18" s="1"/>
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
@@ -2806,9 +2789,8 @@
       <c r="AX18" s="1"/>
       <c r="AY18" s="1"/>
       <c r="AZ18" s="1"/>
-      <c r="BA18" s="1"/>
-    </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
@@ -2894,11 +2876,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF19" s="1"/>
-      <c r="AG19" s="1">
+      <c r="AF19" s="1">
         <f t="shared" si="9"/>
         <v>7.0400000000000009</v>
       </c>
+      <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
@@ -2918,9 +2900,8 @@
       <c r="AX19" s="1"/>
       <c r="AY19" s="1"/>
       <c r="AZ19" s="1"/>
-      <c r="BA19" s="1"/>
-    </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>47</v>
       </c>
@@ -3009,11 +2990,11 @@
         <f t="shared" si="8"/>
         <v>204</v>
       </c>
-      <c r="AF20" s="1"/>
-      <c r="AG20" s="1">
+      <c r="AF20" s="1">
         <f t="shared" si="9"/>
         <v>52.622599999999998</v>
       </c>
+      <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
@@ -3033,9 +3014,8 @@
       <c r="AX20" s="1"/>
       <c r="AY20" s="1"/>
       <c r="AZ20" s="1"/>
-      <c r="BA20" s="1"/>
-    </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,11 +3098,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF21" s="1"/>
-      <c r="AG21" s="1">
+      <c r="AF21" s="1">
         <f t="shared" si="9"/>
         <v>6.7320000000000002</v>
       </c>
+      <c r="AG21" s="1"/>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
@@ -3142,9 +3122,8 @@
       <c r="AX21" s="1"/>
       <c r="AY21" s="1"/>
       <c r="AZ21" s="1"/>
-      <c r="BA21" s="1"/>
-    </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -3221,11 +3200,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF22" s="1"/>
-      <c r="AG22" s="1">
+      <c r="AF22" s="1">
         <f t="shared" si="9"/>
         <v>2.464</v>
       </c>
+      <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
@@ -3245,9 +3224,8 @@
       <c r="AX22" s="1"/>
       <c r="AY22" s="1"/>
       <c r="AZ22" s="1"/>
-      <c r="BA22" s="1"/>
-    </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -3328,11 +3306,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1">
+      <c r="AF23" s="1">
         <f t="shared" si="9"/>
         <v>0.75</v>
       </c>
+      <c r="AG23" s="1"/>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
@@ -3352,9 +3330,8 @@
       <c r="AX23" s="1"/>
       <c r="AY23" s="1"/>
       <c r="AZ23" s="1"/>
-      <c r="BA23" s="1"/>
-    </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>51</v>
       </c>
@@ -3443,11 +3420,11 @@
         <f t="shared" si="8"/>
         <v>204</v>
       </c>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1">
+      <c r="AF24" s="1">
         <f t="shared" si="9"/>
         <v>48.142600000000002</v>
       </c>
+      <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
@@ -3467,9 +3444,8 @@
       <c r="AX24" s="1"/>
       <c r="AY24" s="1"/>
       <c r="AZ24" s="1"/>
-      <c r="BA24" s="1"/>
-    </row>
-    <row r="25" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
@@ -3559,11 +3535,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF25" s="1"/>
-      <c r="AG25" s="1">
+      <c r="AF25" s="1">
         <f t="shared" si="9"/>
         <v>3.5819999999999994</v>
       </c>
+      <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
@@ -3583,9 +3559,8 @@
       <c r="AX25" s="1"/>
       <c r="AY25" s="1"/>
       <c r="AZ25" s="1"/>
-      <c r="BA25" s="1"/>
-    </row>
-    <row r="26" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
@@ -3676,11 +3651,11 @@
         <f t="shared" si="8"/>
         <v>9.36</v>
       </c>
-      <c r="AF26" s="1"/>
-      <c r="AG26" s="1">
+      <c r="AF26" s="1">
         <f t="shared" si="9"/>
         <v>2.2319999999999998</v>
       </c>
+      <c r="AG26" s="1"/>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
@@ -3700,9 +3675,8 @@
       <c r="AX26" s="1"/>
       <c r="AY26" s="1"/>
       <c r="AZ26" s="1"/>
-      <c r="BA26" s="1"/>
-    </row>
-    <row r="27" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
@@ -3793,11 +3767,11 @@
         <f t="shared" si="8"/>
         <v>21.75</v>
       </c>
-      <c r="AF27" s="1"/>
-      <c r="AG27" s="1">
+      <c r="AF27" s="1">
         <f t="shared" si="9"/>
         <v>4.71</v>
       </c>
+      <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
@@ -3817,9 +3791,8 @@
       <c r="AX27" s="1"/>
       <c r="AY27" s="1"/>
       <c r="AZ27" s="1"/>
-      <c r="BA27" s="1"/>
-    </row>
-    <row r="28" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -3910,11 +3883,11 @@
         <f t="shared" si="8"/>
         <v>301</v>
       </c>
-      <c r="AF28" s="1"/>
-      <c r="AG28" s="1">
+      <c r="AF28" s="1">
         <f t="shared" si="9"/>
         <v>71.776199999999989</v>
       </c>
+      <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
@@ -3934,9 +3907,8 @@
       <c r="AX28" s="1"/>
       <c r="AY28" s="1"/>
       <c r="AZ28" s="1"/>
-      <c r="BA28" s="1"/>
-    </row>
-    <row r="29" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
@@ -4019,11 +3991,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF29" s="1"/>
-      <c r="AG29" s="1">
+      <c r="AF29" s="1">
         <f t="shared" si="9"/>
         <v>6.88</v>
       </c>
+      <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
@@ -4043,9 +4015,8 @@
       <c r="AX29" s="1"/>
       <c r="AY29" s="1"/>
       <c r="AZ29" s="1"/>
-      <c r="BA29" s="1"/>
-    </row>
-    <row r="30" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>57</v>
       </c>
@@ -4136,11 +4107,11 @@
         <f t="shared" si="8"/>
         <v>62.800000000000004</v>
       </c>
-      <c r="AF30" s="1"/>
-      <c r="AG30" s="1">
+      <c r="AF30" s="1">
         <f t="shared" si="9"/>
         <v>19.840000000000003</v>
       </c>
+      <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
@@ -4160,9 +4131,8 @@
       <c r="AX30" s="1"/>
       <c r="AY30" s="1"/>
       <c r="AZ30" s="1"/>
-      <c r="BA30" s="1"/>
-    </row>
-    <row r="31" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>58</v>
       </c>
@@ -4251,11 +4221,11 @@
         <f t="shared" si="8"/>
         <v>56.800000000000004</v>
       </c>
-      <c r="AF31" s="1"/>
-      <c r="AG31" s="1">
+      <c r="AF31" s="1">
         <f t="shared" si="9"/>
         <v>15.12</v>
       </c>
+      <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
@@ -4275,9 +4245,8 @@
       <c r="AX31" s="1"/>
       <c r="AY31" s="1"/>
       <c r="AZ31" s="1"/>
-      <c r="BA31" s="1"/>
-    </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,11 +4334,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF32" s="1"/>
-      <c r="AG32" s="1">
+      <c r="AF32" s="1">
         <f t="shared" si="9"/>
         <v>13.840000000000002</v>
       </c>
+      <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
@@ -4389,9 +4358,8 @@
       <c r="AX32" s="1"/>
       <c r="AY32" s="1"/>
       <c r="AZ32" s="1"/>
-      <c r="BA32" s="1"/>
-    </row>
-    <row r="33" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>60</v>
       </c>
@@ -4482,11 +4450,11 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="AF33" s="1"/>
-      <c r="AG33" s="1">
+      <c r="AF33" s="1">
         <f t="shared" si="9"/>
         <v>6.2200000000000006</v>
       </c>
+      <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
@@ -4506,9 +4474,8 @@
       <c r="AX33" s="1"/>
       <c r="AY33" s="1"/>
       <c r="AZ33" s="1"/>
-      <c r="BA33" s="1"/>
-    </row>
-    <row r="34" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>61</v>
       </c>
@@ -4599,11 +4566,11 @@
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="AF34" s="1"/>
-      <c r="AG34" s="1">
+      <c r="AF34" s="1">
         <f t="shared" si="9"/>
         <v>6.66</v>
       </c>
+      <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
@@ -4623,9 +4590,8 @@
       <c r="AX34" s="1"/>
       <c r="AY34" s="1"/>
       <c r="AZ34" s="1"/>
-      <c r="BA34" s="1"/>
-    </row>
-    <row r="35" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>62</v>
       </c>
@@ -4708,11 +4674,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF35" s="1"/>
-      <c r="AG35" s="1">
+      <c r="AF35" s="1">
         <f t="shared" si="9"/>
         <v>0.7400000000000001</v>
       </c>
+      <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
@@ -4732,9 +4698,8 @@
       <c r="AX35" s="1"/>
       <c r="AY35" s="1"/>
       <c r="AZ35" s="1"/>
-      <c r="BA35" s="1"/>
-    </row>
-    <row r="36" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>63</v>
       </c>
@@ -4822,11 +4787,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF36" s="1"/>
-      <c r="AG36" s="1">
+      <c r="AF36" s="1">
         <f t="shared" si="9"/>
         <v>5.28</v>
       </c>
+      <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
@@ -4846,9 +4811,8 @@
       <c r="AX36" s="1"/>
       <c r="AY36" s="1"/>
       <c r="AZ36" s="1"/>
-      <c r="BA36" s="1"/>
-    </row>
-    <row r="37" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>64</v>
       </c>
@@ -4931,11 +4895,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF37" s="1"/>
-      <c r="AG37" s="1">
+      <c r="AF37" s="1">
         <f t="shared" si="9"/>
         <v>4.8</v>
       </c>
+      <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
@@ -4955,9 +4919,8 @@
       <c r="AX37" s="1"/>
       <c r="AY37" s="1"/>
       <c r="AZ37" s="1"/>
-      <c r="BA37" s="1"/>
-    </row>
-    <row r="38" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>65</v>
       </c>
@@ -5048,11 +5011,11 @@
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="AF38" s="1"/>
-      <c r="AG38" s="1">
+      <c r="AF38" s="1">
         <f t="shared" si="9"/>
         <v>25.6296</v>
       </c>
+      <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
@@ -5072,9 +5035,8 @@
       <c r="AX38" s="1"/>
       <c r="AY38" s="1"/>
       <c r="AZ38" s="1"/>
-      <c r="BA38" s="1"/>
-    </row>
-    <row r="39" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>66</v>
       </c>
@@ -5163,11 +5125,11 @@
         <f t="shared" si="8"/>
         <v>95</v>
       </c>
-      <c r="AF39" s="1"/>
-      <c r="AG39" s="1">
+      <c r="AF39" s="1">
         <f t="shared" si="9"/>
         <v>23.713999999999999</v>
       </c>
+      <c r="AG39" s="1"/>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
@@ -5187,9 +5149,8 @@
       <c r="AX39" s="1"/>
       <c r="AY39" s="1"/>
       <c r="AZ39" s="1"/>
-      <c r="BA39" s="1"/>
-    </row>
-    <row r="40" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>67</v>
       </c>
@@ -5277,11 +5238,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF40" s="1"/>
-      <c r="AG40" s="1">
+      <c r="AF40" s="1">
         <f t="shared" si="9"/>
         <v>29.615600000000001</v>
       </c>
+      <c r="AG40" s="1"/>
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
@@ -5301,9 +5262,8 @@
       <c r="AX40" s="1"/>
       <c r="AY40" s="1"/>
       <c r="AZ40" s="1"/>
-      <c r="BA40" s="1"/>
-    </row>
-    <row r="41" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>68</v>
       </c>
@@ -5384,11 +5344,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF41" s="1"/>
-      <c r="AG41" s="1">
+      <c r="AF41" s="1">
         <f t="shared" si="9"/>
         <v>7.35</v>
       </c>
+      <c r="AG41" s="1"/>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
@@ -5408,9 +5368,8 @@
       <c r="AX41" s="1"/>
       <c r="AY41" s="1"/>
       <c r="AZ41" s="1"/>
-      <c r="BA41" s="1"/>
-    </row>
-    <row r="42" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>69</v>
       </c>
@@ -5501,11 +5460,11 @@
         <f t="shared" si="8"/>
         <v>156</v>
       </c>
-      <c r="AF42" s="1"/>
-      <c r="AG42" s="1">
+      <c r="AF42" s="1">
         <f t="shared" si="9"/>
         <v>44.957999999999998</v>
       </c>
+      <c r="AG42" s="1"/>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
@@ -5525,9 +5484,8 @@
       <c r="AX42" s="1"/>
       <c r="AY42" s="1"/>
       <c r="AZ42" s="1"/>
-      <c r="BA42" s="1"/>
-    </row>
-    <row r="43" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>70</v>
       </c>
@@ -5612,11 +5570,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF43" s="1"/>
-      <c r="AG43" s="1">
+      <c r="AF43" s="1">
         <f t="shared" si="9"/>
         <v>6.3599999999999994</v>
       </c>
+      <c r="AG43" s="1"/>
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
@@ -5636,9 +5594,8 @@
       <c r="AX43" s="1"/>
       <c r="AY43" s="1"/>
       <c r="AZ43" s="1"/>
-      <c r="BA43" s="1"/>
-    </row>
-    <row r="44" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>71</v>
       </c>
@@ -5719,11 +5676,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="1">
+      <c r="AF44" s="1">
         <f t="shared" si="9"/>
         <v>13.000399999999999</v>
       </c>
+      <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
@@ -5743,9 +5700,8 @@
       <c r="AX44" s="1"/>
       <c r="AY44" s="1"/>
       <c r="AZ44" s="1"/>
-      <c r="BA44" s="1"/>
-    </row>
-    <row r="45" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>72</v>
       </c>
@@ -5836,11 +5792,11 @@
         <f t="shared" si="8"/>
         <v>258</v>
       </c>
-      <c r="AF45" s="1"/>
-      <c r="AG45" s="1">
+      <c r="AF45" s="1">
         <f t="shared" si="9"/>
         <v>52.787800000000004</v>
       </c>
+      <c r="AG45" s="1"/>
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
@@ -5860,9 +5816,8 @@
       <c r="AX45" s="1"/>
       <c r="AY45" s="1"/>
       <c r="AZ45" s="1"/>
-      <c r="BA45" s="1"/>
-    </row>
-    <row r="46" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>73</v>
       </c>
@@ -5953,11 +5908,11 @@
         <f t="shared" si="8"/>
         <v>39.549999999999997</v>
       </c>
-      <c r="AF46" s="1"/>
-      <c r="AG46" s="1">
+      <c r="AF46" s="1">
         <f t="shared" si="9"/>
         <v>23.029999999999998</v>
       </c>
+      <c r="AG46" s="1"/>
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
@@ -5977,9 +5932,8 @@
       <c r="AX46" s="1"/>
       <c r="AY46" s="1"/>
       <c r="AZ46" s="1"/>
-      <c r="BA46" s="1"/>
-    </row>
-    <row r="47" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>74</v>
       </c>
@@ -6070,11 +6024,11 @@
         <f t="shared" si="8"/>
         <v>31.159999999999997</v>
       </c>
-      <c r="AF47" s="1"/>
-      <c r="AG47" s="1">
+      <c r="AF47" s="1">
         <f t="shared" si="9"/>
         <v>16.973999999999997</v>
       </c>
+      <c r="AG47" s="1"/>
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
@@ -6094,9 +6048,8 @@
       <c r="AX47" s="1"/>
       <c r="AY47" s="1"/>
       <c r="AZ47" s="1"/>
-      <c r="BA47" s="1"/>
-    </row>
-    <row r="48" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>76</v>
       </c>
@@ -6185,11 +6138,11 @@
         <f t="shared" si="8"/>
         <v>56.169999999999995</v>
       </c>
-      <c r="AF48" s="1"/>
-      <c r="AG48" s="1">
+      <c r="AF48" s="1">
         <f t="shared" si="9"/>
         <v>14.677999999999997</v>
       </c>
+      <c r="AG48" s="1"/>
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
@@ -6209,9 +6162,8 @@
       <c r="AX48" s="1"/>
       <c r="AY48" s="1"/>
       <c r="AZ48" s="1"/>
-      <c r="BA48" s="1"/>
-    </row>
-    <row r="49" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>77</v>
       </c>
@@ -6302,11 +6254,11 @@
         <f t="shared" si="8"/>
         <v>47.879999999999995</v>
       </c>
-      <c r="AF49" s="1"/>
-      <c r="AG49" s="1">
+      <c r="AF49" s="1">
         <f t="shared" si="9"/>
         <v>14.975999999999999</v>
       </c>
+      <c r="AG49" s="1"/>
       <c r="AH49" s="1"/>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
@@ -6326,9 +6278,8 @@
       <c r="AX49" s="1"/>
       <c r="AY49" s="1"/>
       <c r="AZ49" s="1"/>
-      <c r="BA49" s="1"/>
-    </row>
-    <row r="50" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>78</v>
       </c>
@@ -6411,11 +6362,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF50" s="1"/>
-      <c r="AG50" s="1">
+      <c r="AF50" s="1">
         <f t="shared" si="9"/>
         <v>5.28</v>
       </c>
+      <c r="AG50" s="1"/>
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
@@ -6435,9 +6386,8 @@
       <c r="AX50" s="1"/>
       <c r="AY50" s="1"/>
       <c r="AZ50" s="1"/>
-      <c r="BA50" s="1"/>
-    </row>
-    <row r="51" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>79</v>
       </c>
@@ -6518,11 +6468,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF51" s="1"/>
-      <c r="AG51" s="1">
+      <c r="AF51" s="1">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
+      <c r="AG51" s="1"/>
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
@@ -6542,9 +6492,8 @@
       <c r="AX51" s="1"/>
       <c r="AY51" s="1"/>
       <c r="AZ51" s="1"/>
-      <c r="BA51" s="1"/>
-    </row>
-    <row r="52" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>80</v>
       </c>
@@ -6629,11 +6578,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF52" s="1"/>
-      <c r="AG52" s="1">
+      <c r="AF52" s="1">
         <f t="shared" si="9"/>
         <v>1.518</v>
       </c>
+      <c r="AG52" s="1"/>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
@@ -6653,9 +6602,8 @@
       <c r="AX52" s="1"/>
       <c r="AY52" s="1"/>
       <c r="AZ52" s="1"/>
-      <c r="BA52" s="1"/>
-    </row>
-    <row r="53" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>81</v>
       </c>
@@ -6742,11 +6690,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF53" s="1"/>
-      <c r="AG53" s="1">
+      <c r="AF53" s="1">
         <f t="shared" si="9"/>
         <v>47.937400000000004</v>
       </c>
+      <c r="AG53" s="1"/>
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
@@ -6766,9 +6714,8 @@
       <c r="AX53" s="1"/>
       <c r="AY53" s="1"/>
       <c r="AZ53" s="1"/>
-      <c r="BA53" s="1"/>
-    </row>
-    <row r="54" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>82</v>
       </c>
@@ -6851,11 +6798,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF54" s="1"/>
-      <c r="AG54" s="1">
+      <c r="AF54" s="1">
         <f t="shared" si="9"/>
         <v>0.42000000000000004</v>
       </c>
+      <c r="AG54" s="1"/>
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
@@ -6875,9 +6822,8 @@
       <c r="AX54" s="1"/>
       <c r="AY54" s="1"/>
       <c r="AZ54" s="1"/>
-      <c r="BA54" s="1"/>
-    </row>
-    <row r="55" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>83</v>
       </c>
@@ -6968,11 +6914,11 @@
         <f t="shared" si="8"/>
         <v>24.400000000000002</v>
       </c>
-      <c r="AF55" s="1"/>
-      <c r="AG55" s="1">
+      <c r="AF55" s="1">
         <f t="shared" si="9"/>
         <v>8.56</v>
       </c>
+      <c r="AG55" s="1"/>
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
@@ -6992,9 +6938,8 @@
       <c r="AX55" s="1"/>
       <c r="AY55" s="1"/>
       <c r="AZ55" s="1"/>
-      <c r="BA55" s="1"/>
-    </row>
-    <row r="56" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>84</v>
       </c>
@@ -7073,11 +7018,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF56" s="1"/>
-      <c r="AG56" s="1">
+      <c r="AF56" s="1">
         <f t="shared" si="9"/>
         <v>6.2573999999999996</v>
       </c>
+      <c r="AG56" s="1"/>
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
@@ -7097,9 +7042,8 @@
       <c r="AX56" s="1"/>
       <c r="AY56" s="1"/>
       <c r="AZ56" s="1"/>
-      <c r="BA56" s="1"/>
-    </row>
-    <row r="57" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>85</v>
       </c>
@@ -7183,11 +7127,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF57" s="1"/>
-      <c r="AG57" s="1">
+      <c r="AF57" s="1">
         <f t="shared" si="9"/>
         <v>6.0140000000000002</v>
       </c>
+      <c r="AG57" s="1"/>
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
@@ -7207,9 +7151,8 @@
       <c r="AX57" s="1"/>
       <c r="AY57" s="1"/>
       <c r="AZ57" s="1"/>
-      <c r="BA57" s="1"/>
-    </row>
-    <row r="58" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>86</v>
       </c>
@@ -7284,11 +7227,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF58" s="1"/>
-      <c r="AG58" s="1">
+      <c r="AF58" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
+      <c r="AG58" s="1"/>
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
@@ -7308,9 +7251,8 @@
       <c r="AX58" s="1"/>
       <c r="AY58" s="1"/>
       <c r="AZ58" s="1"/>
-      <c r="BA58" s="1"/>
-    </row>
-    <row r="59" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>87</v>
       </c>
@@ -7393,11 +7335,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF59" s="1"/>
-      <c r="AG59" s="1">
+      <c r="AF59" s="1">
         <f t="shared" si="9"/>
         <v>1.55</v>
       </c>
+      <c r="AG59" s="1"/>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
@@ -7417,9 +7359,8 @@
       <c r="AX59" s="1"/>
       <c r="AY59" s="1"/>
       <c r="AZ59" s="1"/>
-      <c r="BA59" s="1"/>
-    </row>
-    <row r="60" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>88</v>
       </c>
@@ -7507,11 +7448,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF60" s="1"/>
-      <c r="AG60" s="1">
+      <c r="AF60" s="1">
         <f t="shared" si="9"/>
         <v>10.959999999999999</v>
       </c>
+      <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
@@ -7531,9 +7472,8 @@
       <c r="AX60" s="1"/>
       <c r="AY60" s="1"/>
       <c r="AZ60" s="1"/>
-      <c r="BA60" s="1"/>
-    </row>
-    <row r="61" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>89</v>
       </c>
@@ -7618,11 +7558,11 @@
         <f t="shared" si="8"/>
         <v>25.5</v>
       </c>
-      <c r="AF61" s="1"/>
-      <c r="AG61" s="1">
+      <c r="AF61" s="1">
         <f t="shared" si="9"/>
         <v>11.16</v>
       </c>
+      <c r="AG61" s="1"/>
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
@@ -7642,9 +7582,8 @@
       <c r="AX61" s="1"/>
       <c r="AY61" s="1"/>
       <c r="AZ61" s="1"/>
-      <c r="BA61" s="1"/>
-    </row>
-    <row r="62" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>90</v>
       </c>
@@ -7734,11 +7673,11 @@
         <f t="shared" si="8"/>
         <v>124.63999999999999</v>
       </c>
-      <c r="AF62" s="1"/>
-      <c r="AG62" s="1">
+      <c r="AF62" s="1">
         <f t="shared" si="9"/>
         <v>34.44</v>
       </c>
+      <c r="AG62" s="1"/>
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
@@ -7758,9 +7697,8 @@
       <c r="AX62" s="1"/>
       <c r="AY62" s="1"/>
       <c r="AZ62" s="1"/>
-      <c r="BA62" s="1"/>
-    </row>
-    <row r="63" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>91</v>
       </c>
@@ -7837,11 +7775,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF63" s="1"/>
-      <c r="AG63" s="1">
+      <c r="AF63" s="1">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
+      <c r="AG63" s="1"/>
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
@@ -7861,9 +7799,8 @@
       <c r="AX63" s="1"/>
       <c r="AY63" s="1"/>
       <c r="AZ63" s="1"/>
-      <c r="BA63" s="1"/>
-    </row>
-    <row r="64" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>93</v>
       </c>
@@ -7954,11 +7891,11 @@
         <f t="shared" si="8"/>
         <v>301</v>
       </c>
-      <c r="AF64" s="1"/>
-      <c r="AG64" s="1">
+      <c r="AF64" s="1">
         <f t="shared" si="9"/>
         <v>84.347999999999999</v>
       </c>
+      <c r="AG64" s="1"/>
       <c r="AH64" s="1"/>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
@@ -7978,9 +7915,8 @@
       <c r="AX64" s="1"/>
       <c r="AY64" s="1"/>
       <c r="AZ64" s="1"/>
-      <c r="BA64" s="1"/>
-    </row>
-    <row r="65" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>94</v>
       </c>
@@ -8068,11 +8004,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF65" s="1"/>
-      <c r="AG65" s="1">
+      <c r="AF65" s="1">
         <f t="shared" si="9"/>
         <v>4.4099999999999993</v>
       </c>
+      <c r="AG65" s="1"/>
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
@@ -8092,9 +8028,8 @@
       <c r="AX65" s="1"/>
       <c r="AY65" s="1"/>
       <c r="AZ65" s="1"/>
-      <c r="BA65" s="1"/>
-    </row>
-    <row r="66" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>95</v>
       </c>
@@ -8180,11 +8115,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF66" s="1"/>
-      <c r="AG66" s="1">
+      <c r="AF66" s="1">
         <f t="shared" si="9"/>
         <v>15.461600000000001</v>
       </c>
+      <c r="AG66" s="1"/>
       <c r="AH66" s="1"/>
       <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
@@ -8204,9 +8139,8 @@
       <c r="AX66" s="1"/>
       <c r="AY66" s="1"/>
       <c r="AZ66" s="1"/>
-      <c r="BA66" s="1"/>
-    </row>
-    <row r="67" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>96</v>
       </c>
@@ -8297,11 +8231,11 @@
         <f t="shared" si="8"/>
         <v>95.11999999999999</v>
       </c>
-      <c r="AF67" s="1"/>
-      <c r="AG67" s="1">
+      <c r="AF67" s="1">
         <f t="shared" si="9"/>
         <v>23.206</v>
       </c>
+      <c r="AG67" s="1"/>
       <c r="AH67" s="1"/>
       <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
@@ -8321,9 +8255,8 @@
       <c r="AX67" s="1"/>
       <c r="AY67" s="1"/>
       <c r="AZ67" s="1"/>
-      <c r="BA67" s="1"/>
-    </row>
-    <row r="68" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>97</v>
       </c>
@@ -8412,11 +8345,11 @@
         <f t="shared" si="8"/>
         <v>170</v>
       </c>
-      <c r="AF68" s="1"/>
-      <c r="AG68" s="1">
+      <c r="AF68" s="1">
         <f t="shared" si="9"/>
         <v>40.284599999999998</v>
       </c>
+      <c r="AG68" s="1"/>
       <c r="AH68" s="1"/>
       <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
@@ -8436,9 +8369,8 @@
       <c r="AX68" s="1"/>
       <c r="AY68" s="1"/>
       <c r="AZ68" s="1"/>
-      <c r="BA68" s="1"/>
-    </row>
-    <row r="69" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>98</v>
       </c>
@@ -8526,11 +8458,11 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF69" s="1"/>
-      <c r="AG69" s="1">
+      <c r="AF69" s="1">
         <f t="shared" si="9"/>
         <v>5.76</v>
       </c>
+      <c r="AG69" s="1"/>
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
@@ -8550,9 +8482,8 @@
       <c r="AX69" s="1"/>
       <c r="AY69" s="1"/>
       <c r="AZ69" s="1"/>
-      <c r="BA69" s="1"/>
-    </row>
-    <row r="70" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>99</v>
       </c>
@@ -8643,11 +8574,11 @@
         <f t="shared" si="8"/>
         <v>19.98</v>
       </c>
-      <c r="AF70" s="1"/>
-      <c r="AG70" s="1">
+      <c r="AF70" s="1">
         <f t="shared" si="9"/>
         <v>9.7919999999999998</v>
       </c>
+      <c r="AG70" s="1"/>
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
@@ -8667,9 +8598,8 @@
       <c r="AX70" s="1"/>
       <c r="AY70" s="1"/>
       <c r="AZ70" s="1"/>
-      <c r="BA70" s="1"/>
-    </row>
-    <row r="71" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>100</v>
       </c>
@@ -8755,11 +8685,11 @@
         <f t="shared" ref="AE71:AE94" si="30">G71*S71</f>
         <v>0</v>
       </c>
-      <c r="AF71" s="1"/>
-      <c r="AG71" s="1">
-        <f t="shared" ref="AG71:AG94" si="31">P71*G71</f>
+      <c r="AF71" s="1">
+        <f t="shared" ref="AF71:AF94" si="31">P71*G71</f>
         <v>10.247999999999999</v>
       </c>
+      <c r="AG71" s="1"/>
       <c r="AH71" s="1"/>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
@@ -8779,9 +8709,8 @@
       <c r="AX71" s="1"/>
       <c r="AY71" s="1"/>
       <c r="AZ71" s="1"/>
-      <c r="BA71" s="1"/>
-    </row>
-    <row r="72" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>101</v>
       </c>
@@ -8866,11 +8795,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF72" s="1"/>
-      <c r="AG72" s="1">
+      <c r="AF72" s="1">
         <f t="shared" si="31"/>
         <v>15.329999999999998</v>
       </c>
+      <c r="AG72" s="1"/>
       <c r="AH72" s="1"/>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
@@ -8890,9 +8819,8 @@
       <c r="AX72" s="1"/>
       <c r="AY72" s="1"/>
       <c r="AZ72" s="1"/>
-      <c r="BA72" s="1"/>
-    </row>
-    <row r="73" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>102</v>
       </c>
@@ -8983,11 +8911,11 @@
         <f t="shared" si="30"/>
         <v>124</v>
       </c>
-      <c r="AF73" s="1"/>
-      <c r="AG73" s="1">
+      <c r="AF73" s="1">
         <f t="shared" si="31"/>
         <v>33.808399999999999</v>
       </c>
+      <c r="AG73" s="1"/>
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
@@ -9007,9 +8935,8 @@
       <c r="AX73" s="1"/>
       <c r="AY73" s="1"/>
       <c r="AZ73" s="1"/>
-      <c r="BA73" s="1"/>
-    </row>
-    <row r="74" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>103</v>
       </c>
@@ -9100,11 +9027,11 @@
         <f t="shared" si="30"/>
         <v>218</v>
       </c>
-      <c r="AF74" s="1"/>
-      <c r="AG74" s="1">
+      <c r="AF74" s="1">
         <f t="shared" si="31"/>
         <v>57.070000000000007</v>
       </c>
+      <c r="AG74" s="1"/>
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
@@ -9124,9 +9051,8 @@
       <c r="AX74" s="1"/>
       <c r="AY74" s="1"/>
       <c r="AZ74" s="1"/>
-      <c r="BA74" s="1"/>
-    </row>
-    <row r="75" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>104</v>
       </c>
@@ -9215,11 +9141,11 @@
         <f t="shared" si="30"/>
         <v>61.249999999999993</v>
       </c>
-      <c r="AF75" s="1"/>
-      <c r="AG75" s="1">
+      <c r="AF75" s="1">
         <f t="shared" si="31"/>
         <v>19.669999999999998</v>
       </c>
+      <c r="AG75" s="1"/>
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
@@ -9239,9 +9165,8 @@
       <c r="AX75" s="1"/>
       <c r="AY75" s="1"/>
       <c r="AZ75" s="1"/>
-      <c r="BA75" s="1"/>
-    </row>
-    <row r="76" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>105</v>
       </c>
@@ -9324,11 +9249,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF76" s="1"/>
-      <c r="AG76" s="1">
+      <c r="AF76" s="1">
         <f t="shared" si="31"/>
         <v>2.2200000000000002</v>
       </c>
+      <c r="AG76" s="1"/>
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
@@ -9348,9 +9273,8 @@
       <c r="AX76" s="1"/>
       <c r="AY76" s="1"/>
       <c r="AZ76" s="1"/>
-      <c r="BA76" s="1"/>
-    </row>
-    <row r="77" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>106</v>
       </c>
@@ -9433,11 +9357,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF77" s="1"/>
-      <c r="AG77" s="1">
+      <c r="AF77" s="1">
         <f t="shared" si="31"/>
         <v>1.9799999999999998</v>
       </c>
+      <c r="AG77" s="1"/>
       <c r="AH77" s="1"/>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
@@ -9457,9 +9381,8 @@
       <c r="AX77" s="1"/>
       <c r="AY77" s="1"/>
       <c r="AZ77" s="1"/>
-      <c r="BA77" s="1"/>
-    </row>
-    <row r="78" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>107</v>
       </c>
@@ -9548,11 +9471,11 @@
         <f t="shared" si="30"/>
         <v>47.88</v>
       </c>
-      <c r="AF78" s="1"/>
-      <c r="AG78" s="1">
+      <c r="AF78" s="1">
         <f t="shared" si="31"/>
         <v>11.984</v>
       </c>
+      <c r="AG78" s="1"/>
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
@@ -9572,9 +9495,8 @@
       <c r="AX78" s="1"/>
       <c r="AY78" s="1"/>
       <c r="AZ78" s="1"/>
-      <c r="BA78" s="1"/>
-    </row>
-    <row r="79" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>108</v>
       </c>
@@ -9662,11 +9584,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF79" s="1"/>
-      <c r="AG79" s="1">
+      <c r="AF79" s="1">
         <f t="shared" si="31"/>
         <v>8.4560000000000013</v>
       </c>
+      <c r="AG79" s="1"/>
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1"/>
@@ -9686,9 +9608,8 @@
       <c r="AX79" s="1"/>
       <c r="AY79" s="1"/>
       <c r="AZ79" s="1"/>
-      <c r="BA79" s="1"/>
-    </row>
-    <row r="80" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>109</v>
       </c>
@@ -9774,11 +9695,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF80" s="1"/>
-      <c r="AG80" s="1">
+      <c r="AF80" s="1">
         <f t="shared" si="31"/>
         <v>3.3600000000000003</v>
       </c>
+      <c r="AG80" s="1"/>
       <c r="AH80" s="1"/>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
@@ -9798,9 +9719,8 @@
       <c r="AX80" s="1"/>
       <c r="AY80" s="1"/>
       <c r="AZ80" s="1"/>
-      <c r="BA80" s="1"/>
-    </row>
-    <row r="81" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>110</v>
       </c>
@@ -9891,11 +9811,11 @@
         <f t="shared" si="30"/>
         <v>103.04</v>
       </c>
-      <c r="AF81" s="1"/>
-      <c r="AG81" s="1">
+      <c r="AF81" s="1">
         <f t="shared" si="31"/>
         <v>23.240000000000002</v>
       </c>
+      <c r="AG81" s="1"/>
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
@@ -9915,9 +9835,8 @@
       <c r="AX81" s="1"/>
       <c r="AY81" s="1"/>
       <c r="AZ81" s="1"/>
-      <c r="BA81" s="1"/>
-    </row>
-    <row r="82" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>111</v>
       </c>
@@ -10008,11 +9927,11 @@
         <f t="shared" si="30"/>
         <v>77.600000000000009</v>
       </c>
-      <c r="AF82" s="1"/>
-      <c r="AG82" s="1">
+      <c r="AF82" s="1">
         <f t="shared" si="31"/>
         <v>17.440000000000001</v>
       </c>
+      <c r="AG82" s="1"/>
       <c r="AH82" s="1"/>
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1"/>
@@ -10032,9 +9951,8 @@
       <c r="AX82" s="1"/>
       <c r="AY82" s="1"/>
       <c r="AZ82" s="1"/>
-      <c r="BA82" s="1"/>
-    </row>
-    <row r="83" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>112</v>
       </c>
@@ -10117,11 +10035,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF83" s="1"/>
-      <c r="AG83" s="1">
+      <c r="AF83" s="1">
         <f t="shared" si="31"/>
         <v>2.2799999999999998</v>
       </c>
+      <c r="AG83" s="1"/>
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1"/>
@@ -10141,9 +10059,8 @@
       <c r="AX83" s="1"/>
       <c r="AY83" s="1"/>
       <c r="AZ83" s="1"/>
-      <c r="BA83" s="1"/>
-    </row>
-    <row r="84" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>113</v>
       </c>
@@ -10228,11 +10145,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF84" s="1"/>
-      <c r="AG84" s="1">
+      <c r="AF84" s="1">
         <f t="shared" si="31"/>
         <v>2.1120000000000001</v>
       </c>
+      <c r="AG84" s="1"/>
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
@@ -10252,9 +10169,8 @@
       <c r="AX84" s="1"/>
       <c r="AY84" s="1"/>
       <c r="AZ84" s="1"/>
-      <c r="BA84" s="1"/>
-    </row>
-    <row r="85" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>114</v>
       </c>
@@ -10340,11 +10256,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF85" s="1"/>
-      <c r="AG85" s="1">
+      <c r="AF85" s="1">
         <f t="shared" si="31"/>
         <v>0.8</v>
       </c>
+      <c r="AG85" s="1"/>
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
@@ -10364,9 +10280,8 @@
       <c r="AX85" s="1"/>
       <c r="AY85" s="1"/>
       <c r="AZ85" s="1"/>
-      <c r="BA85" s="1"/>
-    </row>
-    <row r="86" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>115</v>
       </c>
@@ -10449,11 +10364,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF86" s="1"/>
-      <c r="AG86" s="1">
+      <c r="AF86" s="1">
         <f t="shared" si="31"/>
         <v>3.3600000000000003</v>
       </c>
+      <c r="AG86" s="1"/>
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1"/>
@@ -10473,9 +10388,8 @@
       <c r="AX86" s="1"/>
       <c r="AY86" s="1"/>
       <c r="AZ86" s="1"/>
-      <c r="BA86" s="1"/>
-    </row>
-    <row r="87" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>116</v>
       </c>
@@ -10556,11 +10470,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF87" s="1"/>
-      <c r="AG87" s="1">
+      <c r="AF87" s="1">
         <f t="shared" si="31"/>
         <v>2.76</v>
       </c>
+      <c r="AG87" s="1"/>
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
       <c r="AJ87" s="1"/>
@@ -10580,9 +10494,8 @@
       <c r="AX87" s="1"/>
       <c r="AY87" s="1"/>
       <c r="AZ87" s="1"/>
-      <c r="BA87" s="1"/>
-    </row>
-    <row r="88" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>117</v>
       </c>
@@ -10673,11 +10586,11 @@
         <f t="shared" si="30"/>
         <v>14.04</v>
       </c>
-      <c r="AF88" s="1"/>
-      <c r="AG88" s="1">
+      <c r="AF88" s="1">
         <f t="shared" si="31"/>
         <v>2.9279999999999999</v>
       </c>
+      <c r="AG88" s="1"/>
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
@@ -10697,9 +10610,8 @@
       <c r="AX88" s="1"/>
       <c r="AY88" s="1"/>
       <c r="AZ88" s="1"/>
-      <c r="BA88" s="1"/>
-    </row>
-    <row r="89" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
         <v>118</v>
       </c>
@@ -10778,11 +10690,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF89" s="1"/>
-      <c r="AG89" s="1">
+      <c r="AF89" s="1">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
+      <c r="AG89" s="1"/>
       <c r="AH89" s="1"/>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
@@ -10802,9 +10714,8 @@
       <c r="AX89" s="1"/>
       <c r="AY89" s="1"/>
       <c r="AZ89" s="1"/>
-      <c r="BA89" s="1"/>
-    </row>
-    <row r="90" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>119</v>
       </c>
@@ -10883,11 +10794,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF90" s="1"/>
-      <c r="AG90" s="1">
+      <c r="AF90" s="1">
         <f t="shared" si="31"/>
         <v>0.66</v>
       </c>
+      <c r="AG90" s="1"/>
       <c r="AH90" s="1"/>
       <c r="AI90" s="1"/>
       <c r="AJ90" s="1"/>
@@ -10907,9 +10818,8 @@
       <c r="AX90" s="1"/>
       <c r="AY90" s="1"/>
       <c r="AZ90" s="1"/>
-      <c r="BA90" s="1"/>
-    </row>
-    <row r="91" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>120</v>
       </c>
@@ -10986,11 +10896,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF91" s="1"/>
-      <c r="AG91" s="1">
+      <c r="AF91" s="1">
         <f t="shared" si="31"/>
         <v>1.9600000000000002</v>
       </c>
+      <c r="AG91" s="1"/>
       <c r="AH91" s="1"/>
       <c r="AI91" s="1"/>
       <c r="AJ91" s="1"/>
@@ -11010,9 +10920,8 @@
       <c r="AX91" s="1"/>
       <c r="AY91" s="1"/>
       <c r="AZ91" s="1"/>
-      <c r="BA91" s="1"/>
-    </row>
-    <row r="92" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>121</v>
       </c>
@@ -11091,11 +11000,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF92" s="1"/>
-      <c r="AG92" s="1">
+      <c r="AF92" s="1">
         <f t="shared" si="31"/>
         <v>0.96</v>
       </c>
+      <c r="AG92" s="1"/>
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
@@ -11115,9 +11024,8 @@
       <c r="AX92" s="1"/>
       <c r="AY92" s="1"/>
       <c r="AZ92" s="1"/>
-      <c r="BA92" s="1"/>
-    </row>
-    <row r="93" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>122</v>
       </c>
@@ -11198,11 +11106,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF93" s="1"/>
-      <c r="AG93" s="1">
+      <c r="AF93" s="1">
         <f t="shared" si="31"/>
         <v>1.3299999999999998</v>
       </c>
+      <c r="AG93" s="1"/>
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1"/>
@@ -11222,9 +11130,8 @@
       <c r="AX93" s="1"/>
       <c r="AY93" s="1"/>
       <c r="AZ93" s="1"/>
-      <c r="BA93" s="1"/>
-    </row>
-    <row r="94" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>123</v>
       </c>
@@ -11307,11 +11214,11 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AF94" s="1"/>
-      <c r="AG94" s="1">
+      <c r="AF94" s="1">
         <f t="shared" si="31"/>
         <v>1.1220000000000001</v>
       </c>
+      <c r="AG94" s="1"/>
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
@@ -11331,9 +11238,8 @@
       <c r="AX94" s="1"/>
       <c r="AY94" s="1"/>
       <c r="AZ94" s="1"/>
-      <c r="BA94" s="1"/>
-    </row>
-    <row r="95" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -11386,9 +11292,8 @@
       <c r="AX95" s="1"/>
       <c r="AY95" s="1"/>
       <c r="AZ95" s="1"/>
-      <c r="BA95" s="1"/>
-    </row>
-    <row r="96" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -11441,9 +11346,8 @@
       <c r="AX96" s="1"/>
       <c r="AY96" s="1"/>
       <c r="AZ96" s="1"/>
-      <c r="BA96" s="1"/>
-    </row>
-    <row r="97" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -11496,9 +11400,8 @@
       <c r="AX97" s="1"/>
       <c r="AY97" s="1"/>
       <c r="AZ97" s="1"/>
-      <c r="BA97" s="1"/>
-    </row>
-    <row r="98" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -11551,9 +11454,8 @@
       <c r="AX98" s="1"/>
       <c r="AY98" s="1"/>
       <c r="AZ98" s="1"/>
-      <c r="BA98" s="1"/>
-    </row>
-    <row r="99" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -11606,9 +11508,8 @@
       <c r="AX99" s="1"/>
       <c r="AY99" s="1"/>
       <c r="AZ99" s="1"/>
-      <c r="BA99" s="1"/>
-    </row>
-    <row r="100" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -11661,9 +11562,8 @@
       <c r="AX100" s="1"/>
       <c r="AY100" s="1"/>
       <c r="AZ100" s="1"/>
-      <c r="BA100" s="1"/>
-    </row>
-    <row r="101" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -11716,9 +11616,8 @@
       <c r="AX101" s="1"/>
       <c r="AY101" s="1"/>
       <c r="AZ101" s="1"/>
-      <c r="BA101" s="1"/>
-    </row>
-    <row r="102" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -11771,9 +11670,8 @@
       <c r="AX102" s="1"/>
       <c r="AY102" s="1"/>
       <c r="AZ102" s="1"/>
-      <c r="BA102" s="1"/>
-    </row>
-    <row r="103" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -11826,9 +11724,8 @@
       <c r="AX103" s="1"/>
       <c r="AY103" s="1"/>
       <c r="AZ103" s="1"/>
-      <c r="BA103" s="1"/>
-    </row>
-    <row r="104" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -11881,9 +11778,8 @@
       <c r="AX104" s="1"/>
       <c r="AY104" s="1"/>
       <c r="AZ104" s="1"/>
-      <c r="BA104" s="1"/>
-    </row>
-    <row r="105" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -11936,9 +11832,8 @@
       <c r="AX105" s="1"/>
       <c r="AY105" s="1"/>
       <c r="AZ105" s="1"/>
-      <c r="BA105" s="1"/>
-    </row>
-    <row r="106" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -11991,9 +11886,8 @@
       <c r="AX106" s="1"/>
       <c r="AY106" s="1"/>
       <c r="AZ106" s="1"/>
-      <c r="BA106" s="1"/>
-    </row>
-    <row r="107" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -12046,9 +11940,8 @@
       <c r="AX107" s="1"/>
       <c r="AY107" s="1"/>
       <c r="AZ107" s="1"/>
-      <c r="BA107" s="1"/>
-    </row>
-    <row r="108" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -12101,9 +11994,8 @@
       <c r="AX108" s="1"/>
       <c r="AY108" s="1"/>
       <c r="AZ108" s="1"/>
-      <c r="BA108" s="1"/>
-    </row>
-    <row r="109" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -12156,9 +12048,8 @@
       <c r="AX109" s="1"/>
       <c r="AY109" s="1"/>
       <c r="AZ109" s="1"/>
-      <c r="BA109" s="1"/>
-    </row>
-    <row r="110" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -12211,9 +12102,8 @@
       <c r="AX110" s="1"/>
       <c r="AY110" s="1"/>
       <c r="AZ110" s="1"/>
-      <c r="BA110" s="1"/>
-    </row>
-    <row r="111" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -12266,9 +12156,8 @@
       <c r="AX111" s="1"/>
       <c r="AY111" s="1"/>
       <c r="AZ111" s="1"/>
-      <c r="BA111" s="1"/>
-    </row>
-    <row r="112" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -12321,9 +12210,8 @@
       <c r="AX112" s="1"/>
       <c r="AY112" s="1"/>
       <c r="AZ112" s="1"/>
-      <c r="BA112" s="1"/>
-    </row>
-    <row r="113" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -12376,9 +12264,8 @@
       <c r="AX113" s="1"/>
       <c r="AY113" s="1"/>
       <c r="AZ113" s="1"/>
-      <c r="BA113" s="1"/>
-    </row>
-    <row r="114" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -12431,9 +12318,8 @@
       <c r="AX114" s="1"/>
       <c r="AY114" s="1"/>
       <c r="AZ114" s="1"/>
-      <c r="BA114" s="1"/>
-    </row>
-    <row r="115" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -12486,9 +12372,8 @@
       <c r="AX115" s="1"/>
       <c r="AY115" s="1"/>
       <c r="AZ115" s="1"/>
-      <c r="BA115" s="1"/>
-    </row>
-    <row r="116" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -12541,9 +12426,8 @@
       <c r="AX116" s="1"/>
       <c r="AY116" s="1"/>
       <c r="AZ116" s="1"/>
-      <c r="BA116" s="1"/>
-    </row>
-    <row r="117" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -12596,9 +12480,8 @@
       <c r="AX117" s="1"/>
       <c r="AY117" s="1"/>
       <c r="AZ117" s="1"/>
-      <c r="BA117" s="1"/>
-    </row>
-    <row r="118" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -12651,9 +12534,8 @@
       <c r="AX118" s="1"/>
       <c r="AY118" s="1"/>
       <c r="AZ118" s="1"/>
-      <c r="BA118" s="1"/>
-    </row>
-    <row r="119" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -12706,9 +12588,8 @@
       <c r="AX119" s="1"/>
       <c r="AY119" s="1"/>
       <c r="AZ119" s="1"/>
-      <c r="BA119" s="1"/>
-    </row>
-    <row r="120" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -12761,9 +12642,8 @@
       <c r="AX120" s="1"/>
       <c r="AY120" s="1"/>
       <c r="AZ120" s="1"/>
-      <c r="BA120" s="1"/>
-    </row>
-    <row r="121" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -12816,9 +12696,8 @@
       <c r="AX121" s="1"/>
       <c r="AY121" s="1"/>
       <c r="AZ121" s="1"/>
-      <c r="BA121" s="1"/>
-    </row>
-    <row r="122" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -12871,9 +12750,8 @@
       <c r="AX122" s="1"/>
       <c r="AY122" s="1"/>
       <c r="AZ122" s="1"/>
-      <c r="BA122" s="1"/>
-    </row>
-    <row r="123" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -12926,9 +12804,8 @@
       <c r="AX123" s="1"/>
       <c r="AY123" s="1"/>
       <c r="AZ123" s="1"/>
-      <c r="BA123" s="1"/>
-    </row>
-    <row r="124" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -12981,9 +12858,8 @@
       <c r="AX124" s="1"/>
       <c r="AY124" s="1"/>
       <c r="AZ124" s="1"/>
-      <c r="BA124" s="1"/>
-    </row>
-    <row r="125" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -13036,9 +12912,8 @@
       <c r="AX125" s="1"/>
       <c r="AY125" s="1"/>
       <c r="AZ125" s="1"/>
-      <c r="BA125" s="1"/>
-    </row>
-    <row r="126" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -13091,9 +12966,8 @@
       <c r="AX126" s="1"/>
       <c r="AY126" s="1"/>
       <c r="AZ126" s="1"/>
-      <c r="BA126" s="1"/>
-    </row>
-    <row r="127" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -13146,9 +13020,8 @@
       <c r="AX127" s="1"/>
       <c r="AY127" s="1"/>
       <c r="AZ127" s="1"/>
-      <c r="BA127" s="1"/>
-    </row>
-    <row r="128" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -13201,9 +13074,8 @@
       <c r="AX128" s="1"/>
       <c r="AY128" s="1"/>
       <c r="AZ128" s="1"/>
-      <c r="BA128" s="1"/>
-    </row>
-    <row r="129" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -13256,9 +13128,8 @@
       <c r="AX129" s="1"/>
       <c r="AY129" s="1"/>
       <c r="AZ129" s="1"/>
-      <c r="BA129" s="1"/>
-    </row>
-    <row r="130" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -13311,9 +13182,8 @@
       <c r="AX130" s="1"/>
       <c r="AY130" s="1"/>
       <c r="AZ130" s="1"/>
-      <c r="BA130" s="1"/>
-    </row>
-    <row r="131" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -13366,9 +13236,8 @@
       <c r="AX131" s="1"/>
       <c r="AY131" s="1"/>
       <c r="AZ131" s="1"/>
-      <c r="BA131" s="1"/>
-    </row>
-    <row r="132" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -13421,9 +13290,8 @@
       <c r="AX132" s="1"/>
       <c r="AY132" s="1"/>
       <c r="AZ132" s="1"/>
-      <c r="BA132" s="1"/>
-    </row>
-    <row r="133" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -13476,9 +13344,8 @@
       <c r="AX133" s="1"/>
       <c r="AY133" s="1"/>
       <c r="AZ133" s="1"/>
-      <c r="BA133" s="1"/>
-    </row>
-    <row r="134" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -13531,9 +13398,8 @@
       <c r="AX134" s="1"/>
       <c r="AY134" s="1"/>
       <c r="AZ134" s="1"/>
-      <c r="BA134" s="1"/>
-    </row>
-    <row r="135" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -13586,9 +13452,8 @@
       <c r="AX135" s="1"/>
       <c r="AY135" s="1"/>
       <c r="AZ135" s="1"/>
-      <c r="BA135" s="1"/>
-    </row>
-    <row r="136" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -13641,9 +13506,8 @@
       <c r="AX136" s="1"/>
       <c r="AY136" s="1"/>
       <c r="AZ136" s="1"/>
-      <c r="BA136" s="1"/>
-    </row>
-    <row r="137" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -13696,9 +13560,8 @@
       <c r="AX137" s="1"/>
       <c r="AY137" s="1"/>
       <c r="AZ137" s="1"/>
-      <c r="BA137" s="1"/>
-    </row>
-    <row r="138" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -13751,9 +13614,8 @@
       <c r="AX138" s="1"/>
       <c r="AY138" s="1"/>
       <c r="AZ138" s="1"/>
-      <c r="BA138" s="1"/>
-    </row>
-    <row r="139" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -13806,9 +13668,8 @@
       <c r="AX139" s="1"/>
       <c r="AY139" s="1"/>
       <c r="AZ139" s="1"/>
-      <c r="BA139" s="1"/>
-    </row>
-    <row r="140" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -13861,9 +13722,8 @@
       <c r="AX140" s="1"/>
       <c r="AY140" s="1"/>
       <c r="AZ140" s="1"/>
-      <c r="BA140" s="1"/>
-    </row>
-    <row r="141" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -13916,9 +13776,8 @@
       <c r="AX141" s="1"/>
       <c r="AY141" s="1"/>
       <c r="AZ141" s="1"/>
-      <c r="BA141" s="1"/>
-    </row>
-    <row r="142" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -13971,9 +13830,8 @@
       <c r="AX142" s="1"/>
       <c r="AY142" s="1"/>
       <c r="AZ142" s="1"/>
-      <c r="BA142" s="1"/>
-    </row>
-    <row r="143" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -14026,9 +13884,8 @@
       <c r="AX143" s="1"/>
       <c r="AY143" s="1"/>
       <c r="AZ143" s="1"/>
-      <c r="BA143" s="1"/>
-    </row>
-    <row r="144" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -14081,9 +13938,8 @@
       <c r="AX144" s="1"/>
       <c r="AY144" s="1"/>
       <c r="AZ144" s="1"/>
-      <c r="BA144" s="1"/>
-    </row>
-    <row r="145" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -14136,9 +13992,8 @@
       <c r="AX145" s="1"/>
       <c r="AY145" s="1"/>
       <c r="AZ145" s="1"/>
-      <c r="BA145" s="1"/>
-    </row>
-    <row r="146" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -14191,9 +14046,8 @@
       <c r="AX146" s="1"/>
       <c r="AY146" s="1"/>
       <c r="AZ146" s="1"/>
-      <c r="BA146" s="1"/>
-    </row>
-    <row r="147" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -14246,9 +14100,8 @@
       <c r="AX147" s="1"/>
       <c r="AY147" s="1"/>
       <c r="AZ147" s="1"/>
-      <c r="BA147" s="1"/>
-    </row>
-    <row r="148" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -14301,9 +14154,8 @@
       <c r="AX148" s="1"/>
       <c r="AY148" s="1"/>
       <c r="AZ148" s="1"/>
-      <c r="BA148" s="1"/>
-    </row>
-    <row r="149" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -14356,9 +14208,8 @@
       <c r="AX149" s="1"/>
       <c r="AY149" s="1"/>
       <c r="AZ149" s="1"/>
-      <c r="BA149" s="1"/>
-    </row>
-    <row r="150" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -14411,9 +14262,8 @@
       <c r="AX150" s="1"/>
       <c r="AY150" s="1"/>
       <c r="AZ150" s="1"/>
-      <c r="BA150" s="1"/>
-    </row>
-    <row r="151" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -14466,9 +14316,8 @@
       <c r="AX151" s="1"/>
       <c r="AY151" s="1"/>
       <c r="AZ151" s="1"/>
-      <c r="BA151" s="1"/>
-    </row>
-    <row r="152" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -14521,9 +14370,8 @@
       <c r="AX152" s="1"/>
       <c r="AY152" s="1"/>
       <c r="AZ152" s="1"/>
-      <c r="BA152" s="1"/>
-    </row>
-    <row r="153" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -14576,9 +14424,8 @@
       <c r="AX153" s="1"/>
       <c r="AY153" s="1"/>
       <c r="AZ153" s="1"/>
-      <c r="BA153" s="1"/>
-    </row>
-    <row r="154" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -14631,9 +14478,8 @@
       <c r="AX154" s="1"/>
       <c r="AY154" s="1"/>
       <c r="AZ154" s="1"/>
-      <c r="BA154" s="1"/>
-    </row>
-    <row r="155" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -14686,9 +14532,8 @@
       <c r="AX155" s="1"/>
       <c r="AY155" s="1"/>
       <c r="AZ155" s="1"/>
-      <c r="BA155" s="1"/>
-    </row>
-    <row r="156" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -14741,9 +14586,8 @@
       <c r="AX156" s="1"/>
       <c r="AY156" s="1"/>
       <c r="AZ156" s="1"/>
-      <c r="BA156" s="1"/>
-    </row>
-    <row r="157" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -14796,9 +14640,8 @@
       <c r="AX157" s="1"/>
       <c r="AY157" s="1"/>
       <c r="AZ157" s="1"/>
-      <c r="BA157" s="1"/>
-    </row>
-    <row r="158" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -14851,9 +14694,8 @@
       <c r="AX158" s="1"/>
       <c r="AY158" s="1"/>
       <c r="AZ158" s="1"/>
-      <c r="BA158" s="1"/>
-    </row>
-    <row r="159" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -14906,9 +14748,8 @@
       <c r="AX159" s="1"/>
       <c r="AY159" s="1"/>
       <c r="AZ159" s="1"/>
-      <c r="BA159" s="1"/>
-    </row>
-    <row r="160" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -14961,9 +14802,8 @@
       <c r="AX160" s="1"/>
       <c r="AY160" s="1"/>
       <c r="AZ160" s="1"/>
-      <c r="BA160" s="1"/>
-    </row>
-    <row r="161" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -15016,9 +14856,8 @@
       <c r="AX161" s="1"/>
       <c r="AY161" s="1"/>
       <c r="AZ161" s="1"/>
-      <c r="BA161" s="1"/>
-    </row>
-    <row r="162" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -15071,9 +14910,8 @@
       <c r="AX162" s="1"/>
       <c r="AY162" s="1"/>
       <c r="AZ162" s="1"/>
-      <c r="BA162" s="1"/>
-    </row>
-    <row r="163" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -15126,9 +14964,8 @@
       <c r="AX163" s="1"/>
       <c r="AY163" s="1"/>
       <c r="AZ163" s="1"/>
-      <c r="BA163" s="1"/>
-    </row>
-    <row r="164" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -15181,9 +15018,8 @@
       <c r="AX164" s="1"/>
       <c r="AY164" s="1"/>
       <c r="AZ164" s="1"/>
-      <c r="BA164" s="1"/>
-    </row>
-    <row r="165" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -15236,9 +15072,8 @@
       <c r="AX165" s="1"/>
       <c r="AY165" s="1"/>
       <c r="AZ165" s="1"/>
-      <c r="BA165" s="1"/>
-    </row>
-    <row r="166" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -15291,9 +15126,8 @@
       <c r="AX166" s="1"/>
       <c r="AY166" s="1"/>
       <c r="AZ166" s="1"/>
-      <c r="BA166" s="1"/>
-    </row>
-    <row r="167" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -15346,9 +15180,8 @@
       <c r="AX167" s="1"/>
       <c r="AY167" s="1"/>
       <c r="AZ167" s="1"/>
-      <c r="BA167" s="1"/>
-    </row>
-    <row r="168" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -15401,9 +15234,8 @@
       <c r="AX168" s="1"/>
       <c r="AY168" s="1"/>
       <c r="AZ168" s="1"/>
-      <c r="BA168" s="1"/>
-    </row>
-    <row r="169" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -15456,9 +15288,8 @@
       <c r="AX169" s="1"/>
       <c r="AY169" s="1"/>
       <c r="AZ169" s="1"/>
-      <c r="BA169" s="1"/>
-    </row>
-    <row r="170" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -15511,9 +15342,8 @@
       <c r="AX170" s="1"/>
       <c r="AY170" s="1"/>
       <c r="AZ170" s="1"/>
-      <c r="BA170" s="1"/>
-    </row>
-    <row r="171" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -15566,9 +15396,8 @@
       <c r="AX171" s="1"/>
       <c r="AY171" s="1"/>
       <c r="AZ171" s="1"/>
-      <c r="BA171" s="1"/>
-    </row>
-    <row r="172" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -15621,9 +15450,8 @@
       <c r="AX172" s="1"/>
       <c r="AY172" s="1"/>
       <c r="AZ172" s="1"/>
-      <c r="BA172" s="1"/>
-    </row>
-    <row r="173" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -15676,9 +15504,8 @@
       <c r="AX173" s="1"/>
       <c r="AY173" s="1"/>
       <c r="AZ173" s="1"/>
-      <c r="BA173" s="1"/>
-    </row>
-    <row r="174" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -15731,9 +15558,8 @@
       <c r="AX174" s="1"/>
       <c r="AY174" s="1"/>
       <c r="AZ174" s="1"/>
-      <c r="BA174" s="1"/>
-    </row>
-    <row r="175" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -15786,9 +15612,8 @@
       <c r="AX175" s="1"/>
       <c r="AY175" s="1"/>
       <c r="AZ175" s="1"/>
-      <c r="BA175" s="1"/>
-    </row>
-    <row r="176" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -15841,9 +15666,8 @@
       <c r="AX176" s="1"/>
       <c r="AY176" s="1"/>
       <c r="AZ176" s="1"/>
-      <c r="BA176" s="1"/>
-    </row>
-    <row r="177" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -15896,9 +15720,8 @@
       <c r="AX177" s="1"/>
       <c r="AY177" s="1"/>
       <c r="AZ177" s="1"/>
-      <c r="BA177" s="1"/>
-    </row>
-    <row r="178" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -15951,9 +15774,8 @@
       <c r="AX178" s="1"/>
       <c r="AY178" s="1"/>
       <c r="AZ178" s="1"/>
-      <c r="BA178" s="1"/>
-    </row>
-    <row r="179" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -16006,9 +15828,8 @@
       <c r="AX179" s="1"/>
       <c r="AY179" s="1"/>
       <c r="AZ179" s="1"/>
-      <c r="BA179" s="1"/>
-    </row>
-    <row r="180" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -16061,9 +15882,8 @@
       <c r="AX180" s="1"/>
       <c r="AY180" s="1"/>
       <c r="AZ180" s="1"/>
-      <c r="BA180" s="1"/>
-    </row>
-    <row r="181" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -16116,9 +15936,8 @@
       <c r="AX181" s="1"/>
       <c r="AY181" s="1"/>
       <c r="AZ181" s="1"/>
-      <c r="BA181" s="1"/>
-    </row>
-    <row r="182" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -16171,9 +15990,8 @@
       <c r="AX182" s="1"/>
       <c r="AY182" s="1"/>
       <c r="AZ182" s="1"/>
-      <c r="BA182" s="1"/>
-    </row>
-    <row r="183" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -16226,9 +16044,8 @@
       <c r="AX183" s="1"/>
       <c r="AY183" s="1"/>
       <c r="AZ183" s="1"/>
-      <c r="BA183" s="1"/>
-    </row>
-    <row r="184" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -16281,9 +16098,8 @@
       <c r="AX184" s="1"/>
       <c r="AY184" s="1"/>
       <c r="AZ184" s="1"/>
-      <c r="BA184" s="1"/>
-    </row>
-    <row r="185" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -16336,9 +16152,8 @@
       <c r="AX185" s="1"/>
       <c r="AY185" s="1"/>
       <c r="AZ185" s="1"/>
-      <c r="BA185" s="1"/>
-    </row>
-    <row r="186" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -16391,9 +16206,8 @@
       <c r="AX186" s="1"/>
       <c r="AY186" s="1"/>
       <c r="AZ186" s="1"/>
-      <c r="BA186" s="1"/>
-    </row>
-    <row r="187" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -16446,9 +16260,8 @@
       <c r="AX187" s="1"/>
       <c r="AY187" s="1"/>
       <c r="AZ187" s="1"/>
-      <c r="BA187" s="1"/>
-    </row>
-    <row r="188" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -16501,9 +16314,8 @@
       <c r="AX188" s="1"/>
       <c r="AY188" s="1"/>
       <c r="AZ188" s="1"/>
-      <c r="BA188" s="1"/>
-    </row>
-    <row r="189" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -16556,9 +16368,8 @@
       <c r="AX189" s="1"/>
       <c r="AY189" s="1"/>
       <c r="AZ189" s="1"/>
-      <c r="BA189" s="1"/>
-    </row>
-    <row r="190" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -16611,9 +16422,8 @@
       <c r="AX190" s="1"/>
       <c r="AY190" s="1"/>
       <c r="AZ190" s="1"/>
-      <c r="BA190" s="1"/>
-    </row>
-    <row r="191" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -16666,9 +16476,8 @@
       <c r="AX191" s="1"/>
       <c r="AY191" s="1"/>
       <c r="AZ191" s="1"/>
-      <c r="BA191" s="1"/>
-    </row>
-    <row r="192" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -16721,9 +16530,8 @@
       <c r="AX192" s="1"/>
       <c r="AY192" s="1"/>
       <c r="AZ192" s="1"/>
-      <c r="BA192" s="1"/>
-    </row>
-    <row r="193" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -16776,9 +16584,8 @@
       <c r="AX193" s="1"/>
       <c r="AY193" s="1"/>
       <c r="AZ193" s="1"/>
-      <c r="BA193" s="1"/>
-    </row>
-    <row r="194" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -16831,9 +16638,8 @@
       <c r="AX194" s="1"/>
       <c r="AY194" s="1"/>
       <c r="AZ194" s="1"/>
-      <c r="BA194" s="1"/>
-    </row>
-    <row r="195" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -16886,9 +16692,8 @@
       <c r="AX195" s="1"/>
       <c r="AY195" s="1"/>
       <c r="AZ195" s="1"/>
-      <c r="BA195" s="1"/>
-    </row>
-    <row r="196" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -16941,9 +16746,8 @@
       <c r="AX196" s="1"/>
       <c r="AY196" s="1"/>
       <c r="AZ196" s="1"/>
-      <c r="BA196" s="1"/>
-    </row>
-    <row r="197" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -16996,9 +16800,8 @@
       <c r="AX197" s="1"/>
       <c r="AY197" s="1"/>
       <c r="AZ197" s="1"/>
-      <c r="BA197" s="1"/>
-    </row>
-    <row r="198" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -17051,9 +16854,8 @@
       <c r="AX198" s="1"/>
       <c r="AY198" s="1"/>
       <c r="AZ198" s="1"/>
-      <c r="BA198" s="1"/>
-    </row>
-    <row r="199" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -17106,9 +16908,8 @@
       <c r="AX199" s="1"/>
       <c r="AY199" s="1"/>
       <c r="AZ199" s="1"/>
-      <c r="BA199" s="1"/>
-    </row>
-    <row r="200" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -17161,9 +16962,8 @@
       <c r="AX200" s="1"/>
       <c r="AY200" s="1"/>
       <c r="AZ200" s="1"/>
-      <c r="BA200" s="1"/>
-    </row>
-    <row r="201" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -17216,9 +17016,8 @@
       <c r="AX201" s="1"/>
       <c r="AY201" s="1"/>
       <c r="AZ201" s="1"/>
-      <c r="BA201" s="1"/>
-    </row>
-    <row r="202" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -17271,9 +17070,8 @@
       <c r="AX202" s="1"/>
       <c r="AY202" s="1"/>
       <c r="AZ202" s="1"/>
-      <c r="BA202" s="1"/>
-    </row>
-    <row r="203" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -17326,9 +17124,8 @@
       <c r="AX203" s="1"/>
       <c r="AY203" s="1"/>
       <c r="AZ203" s="1"/>
-      <c r="BA203" s="1"/>
-    </row>
-    <row r="204" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -17381,9 +17178,8 @@
       <c r="AX204" s="1"/>
       <c r="AY204" s="1"/>
       <c r="AZ204" s="1"/>
-      <c r="BA204" s="1"/>
-    </row>
-    <row r="205" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -17436,9 +17232,8 @@
       <c r="AX205" s="1"/>
       <c r="AY205" s="1"/>
       <c r="AZ205" s="1"/>
-      <c r="BA205" s="1"/>
-    </row>
-    <row r="206" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -17491,9 +17286,8 @@
       <c r="AX206" s="1"/>
       <c r="AY206" s="1"/>
       <c r="AZ206" s="1"/>
-      <c r="BA206" s="1"/>
-    </row>
-    <row r="207" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -17546,9 +17340,8 @@
       <c r="AX207" s="1"/>
       <c r="AY207" s="1"/>
       <c r="AZ207" s="1"/>
-      <c r="BA207" s="1"/>
-    </row>
-    <row r="208" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -17601,9 +17394,8 @@
       <c r="AX208" s="1"/>
       <c r="AY208" s="1"/>
       <c r="AZ208" s="1"/>
-      <c r="BA208" s="1"/>
-    </row>
-    <row r="209" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -17656,9 +17448,8 @@
       <c r="AX209" s="1"/>
       <c r="AY209" s="1"/>
       <c r="AZ209" s="1"/>
-      <c r="BA209" s="1"/>
-    </row>
-    <row r="210" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -17711,9 +17502,8 @@
       <c r="AX210" s="1"/>
       <c r="AY210" s="1"/>
       <c r="AZ210" s="1"/>
-      <c r="BA210" s="1"/>
-    </row>
-    <row r="211" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -17766,9 +17556,8 @@
       <c r="AX211" s="1"/>
       <c r="AY211" s="1"/>
       <c r="AZ211" s="1"/>
-      <c r="BA211" s="1"/>
-    </row>
-    <row r="212" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -17821,9 +17610,8 @@
       <c r="AX212" s="1"/>
       <c r="AY212" s="1"/>
       <c r="AZ212" s="1"/>
-      <c r="BA212" s="1"/>
-    </row>
-    <row r="213" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -17876,9 +17664,8 @@
       <c r="AX213" s="1"/>
       <c r="AY213" s="1"/>
       <c r="AZ213" s="1"/>
-      <c r="BA213" s="1"/>
-    </row>
-    <row r="214" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -17931,9 +17718,8 @@
       <c r="AX214" s="1"/>
       <c r="AY214" s="1"/>
       <c r="AZ214" s="1"/>
-      <c r="BA214" s="1"/>
-    </row>
-    <row r="215" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -17986,9 +17772,8 @@
       <c r="AX215" s="1"/>
       <c r="AY215" s="1"/>
       <c r="AZ215" s="1"/>
-      <c r="BA215" s="1"/>
-    </row>
-    <row r="216" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -18041,9 +17826,8 @@
       <c r="AX216" s="1"/>
       <c r="AY216" s="1"/>
       <c r="AZ216" s="1"/>
-      <c r="BA216" s="1"/>
-    </row>
-    <row r="217" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -18096,9 +17880,8 @@
       <c r="AX217" s="1"/>
       <c r="AY217" s="1"/>
       <c r="AZ217" s="1"/>
-      <c r="BA217" s="1"/>
-    </row>
-    <row r="218" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -18151,9 +17934,8 @@
       <c r="AX218" s="1"/>
       <c r="AY218" s="1"/>
       <c r="AZ218" s="1"/>
-      <c r="BA218" s="1"/>
-    </row>
-    <row r="219" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -18206,9 +17988,8 @@
       <c r="AX219" s="1"/>
       <c r="AY219" s="1"/>
       <c r="AZ219" s="1"/>
-      <c r="BA219" s="1"/>
-    </row>
-    <row r="220" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -18261,9 +18042,8 @@
       <c r="AX220" s="1"/>
       <c r="AY220" s="1"/>
       <c r="AZ220" s="1"/>
-      <c r="BA220" s="1"/>
-    </row>
-    <row r="221" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -18316,9 +18096,8 @@
       <c r="AX221" s="1"/>
       <c r="AY221" s="1"/>
       <c r="AZ221" s="1"/>
-      <c r="BA221" s="1"/>
-    </row>
-    <row r="222" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -18371,9 +18150,8 @@
       <c r="AX222" s="1"/>
       <c r="AY222" s="1"/>
       <c r="AZ222" s="1"/>
-      <c r="BA222" s="1"/>
-    </row>
-    <row r="223" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -18426,9 +18204,8 @@
       <c r="AX223" s="1"/>
       <c r="AY223" s="1"/>
       <c r="AZ223" s="1"/>
-      <c r="BA223" s="1"/>
-    </row>
-    <row r="224" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -18481,9 +18258,8 @@
       <c r="AX224" s="1"/>
       <c r="AY224" s="1"/>
       <c r="AZ224" s="1"/>
-      <c r="BA224" s="1"/>
-    </row>
-    <row r="225" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -18536,9 +18312,8 @@
       <c r="AX225" s="1"/>
       <c r="AY225" s="1"/>
       <c r="AZ225" s="1"/>
-      <c r="BA225" s="1"/>
-    </row>
-    <row r="226" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -18591,9 +18366,8 @@
       <c r="AX226" s="1"/>
       <c r="AY226" s="1"/>
       <c r="AZ226" s="1"/>
-      <c r="BA226" s="1"/>
-    </row>
-    <row r="227" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -18646,9 +18420,8 @@
       <c r="AX227" s="1"/>
       <c r="AY227" s="1"/>
       <c r="AZ227" s="1"/>
-      <c r="BA227" s="1"/>
-    </row>
-    <row r="228" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -18701,9 +18474,8 @@
       <c r="AX228" s="1"/>
       <c r="AY228" s="1"/>
       <c r="AZ228" s="1"/>
-      <c r="BA228" s="1"/>
-    </row>
-    <row r="229" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -18756,9 +18528,8 @@
       <c r="AX229" s="1"/>
       <c r="AY229" s="1"/>
       <c r="AZ229" s="1"/>
-      <c r="BA229" s="1"/>
-    </row>
-    <row r="230" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -18811,9 +18582,8 @@
       <c r="AX230" s="1"/>
       <c r="AY230" s="1"/>
       <c r="AZ230" s="1"/>
-      <c r="BA230" s="1"/>
-    </row>
-    <row r="231" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -18866,9 +18636,8 @@
       <c r="AX231" s="1"/>
       <c r="AY231" s="1"/>
       <c r="AZ231" s="1"/>
-      <c r="BA231" s="1"/>
-    </row>
-    <row r="232" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -18921,9 +18690,8 @@
       <c r="AX232" s="1"/>
       <c r="AY232" s="1"/>
       <c r="AZ232" s="1"/>
-      <c r="BA232" s="1"/>
-    </row>
-    <row r="233" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -18976,9 +18744,8 @@
       <c r="AX233" s="1"/>
       <c r="AY233" s="1"/>
       <c r="AZ233" s="1"/>
-      <c r="BA233" s="1"/>
-    </row>
-    <row r="234" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -19031,9 +18798,8 @@
       <c r="AX234" s="1"/>
       <c r="AY234" s="1"/>
       <c r="AZ234" s="1"/>
-      <c r="BA234" s="1"/>
-    </row>
-    <row r="235" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -19086,9 +18852,8 @@
       <c r="AX235" s="1"/>
       <c r="AY235" s="1"/>
       <c r="AZ235" s="1"/>
-      <c r="BA235" s="1"/>
-    </row>
-    <row r="236" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -19141,9 +18906,8 @@
       <c r="AX236" s="1"/>
       <c r="AY236" s="1"/>
       <c r="AZ236" s="1"/>
-      <c r="BA236" s="1"/>
-    </row>
-    <row r="237" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -19196,9 +18960,8 @@
       <c r="AX237" s="1"/>
       <c r="AY237" s="1"/>
       <c r="AZ237" s="1"/>
-      <c r="BA237" s="1"/>
-    </row>
-    <row r="238" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -19251,9 +19014,8 @@
       <c r="AX238" s="1"/>
       <c r="AY238" s="1"/>
       <c r="AZ238" s="1"/>
-      <c r="BA238" s="1"/>
-    </row>
-    <row r="239" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -19306,9 +19068,8 @@
       <c r="AX239" s="1"/>
       <c r="AY239" s="1"/>
       <c r="AZ239" s="1"/>
-      <c r="BA239" s="1"/>
-    </row>
-    <row r="240" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -19361,9 +19122,8 @@
       <c r="AX240" s="1"/>
       <c r="AY240" s="1"/>
       <c r="AZ240" s="1"/>
-      <c r="BA240" s="1"/>
-    </row>
-    <row r="241" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -19416,9 +19176,8 @@
       <c r="AX241" s="1"/>
       <c r="AY241" s="1"/>
       <c r="AZ241" s="1"/>
-      <c r="BA241" s="1"/>
-    </row>
-    <row r="242" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -19471,9 +19230,8 @@
       <c r="AX242" s="1"/>
       <c r="AY242" s="1"/>
       <c r="AZ242" s="1"/>
-      <c r="BA242" s="1"/>
-    </row>
-    <row r="243" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -19526,9 +19284,8 @@
       <c r="AX243" s="1"/>
       <c r="AY243" s="1"/>
       <c r="AZ243" s="1"/>
-      <c r="BA243" s="1"/>
-    </row>
-    <row r="244" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -19581,9 +19338,8 @@
       <c r="AX244" s="1"/>
       <c r="AY244" s="1"/>
       <c r="AZ244" s="1"/>
-      <c r="BA244" s="1"/>
-    </row>
-    <row r="245" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -19636,9 +19392,8 @@
       <c r="AX245" s="1"/>
       <c r="AY245" s="1"/>
       <c r="AZ245" s="1"/>
-      <c r="BA245" s="1"/>
-    </row>
-    <row r="246" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -19691,9 +19446,8 @@
       <c r="AX246" s="1"/>
       <c r="AY246" s="1"/>
       <c r="AZ246" s="1"/>
-      <c r="BA246" s="1"/>
-    </row>
-    <row r="247" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -19746,9 +19500,8 @@
       <c r="AX247" s="1"/>
       <c r="AY247" s="1"/>
       <c r="AZ247" s="1"/>
-      <c r="BA247" s="1"/>
-    </row>
-    <row r="248" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -19801,9 +19554,8 @@
       <c r="AX248" s="1"/>
       <c r="AY248" s="1"/>
       <c r="AZ248" s="1"/>
-      <c r="BA248" s="1"/>
-    </row>
-    <row r="249" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -19856,9 +19608,8 @@
       <c r="AX249" s="1"/>
       <c r="AY249" s="1"/>
       <c r="AZ249" s="1"/>
-      <c r="BA249" s="1"/>
-    </row>
-    <row r="250" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -19911,9 +19662,8 @@
       <c r="AX250" s="1"/>
       <c r="AY250" s="1"/>
       <c r="AZ250" s="1"/>
-      <c r="BA250" s="1"/>
-    </row>
-    <row r="251" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -19966,9 +19716,8 @@
       <c r="AX251" s="1"/>
       <c r="AY251" s="1"/>
       <c r="AZ251" s="1"/>
-      <c r="BA251" s="1"/>
-    </row>
-    <row r="252" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -20021,9 +19770,8 @@
       <c r="AX252" s="1"/>
       <c r="AY252" s="1"/>
       <c r="AZ252" s="1"/>
-      <c r="BA252" s="1"/>
-    </row>
-    <row r="253" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -20076,9 +19824,8 @@
       <c r="AX253" s="1"/>
       <c r="AY253" s="1"/>
       <c r="AZ253" s="1"/>
-      <c r="BA253" s="1"/>
-    </row>
-    <row r="254" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -20131,9 +19878,8 @@
       <c r="AX254" s="1"/>
       <c r="AY254" s="1"/>
       <c r="AZ254" s="1"/>
-      <c r="BA254" s="1"/>
-    </row>
-    <row r="255" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -20186,9 +19932,8 @@
       <c r="AX255" s="1"/>
       <c r="AY255" s="1"/>
       <c r="AZ255" s="1"/>
-      <c r="BA255" s="1"/>
-    </row>
-    <row r="256" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -20241,9 +19986,8 @@
       <c r="AX256" s="1"/>
       <c r="AY256" s="1"/>
       <c r="AZ256" s="1"/>
-      <c r="BA256" s="1"/>
-    </row>
-    <row r="257" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -20296,9 +20040,8 @@
       <c r="AX257" s="1"/>
       <c r="AY257" s="1"/>
       <c r="AZ257" s="1"/>
-      <c r="BA257" s="1"/>
-    </row>
-    <row r="258" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -20351,9 +20094,8 @@
       <c r="AX258" s="1"/>
       <c r="AY258" s="1"/>
       <c r="AZ258" s="1"/>
-      <c r="BA258" s="1"/>
-    </row>
-    <row r="259" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -20406,9 +20148,8 @@
       <c r="AX259" s="1"/>
       <c r="AY259" s="1"/>
       <c r="AZ259" s="1"/>
-      <c r="BA259" s="1"/>
-    </row>
-    <row r="260" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -20461,9 +20202,8 @@
       <c r="AX260" s="1"/>
       <c r="AY260" s="1"/>
       <c r="AZ260" s="1"/>
-      <c r="BA260" s="1"/>
-    </row>
-    <row r="261" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -20516,9 +20256,8 @@
       <c r="AX261" s="1"/>
       <c r="AY261" s="1"/>
       <c r="AZ261" s="1"/>
-      <c r="BA261" s="1"/>
-    </row>
-    <row r="262" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -20571,9 +20310,8 @@
       <c r="AX262" s="1"/>
       <c r="AY262" s="1"/>
       <c r="AZ262" s="1"/>
-      <c r="BA262" s="1"/>
-    </row>
-    <row r="263" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -20626,9 +20364,8 @@
       <c r="AX263" s="1"/>
       <c r="AY263" s="1"/>
       <c r="AZ263" s="1"/>
-      <c r="BA263" s="1"/>
-    </row>
-    <row r="264" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -20681,9 +20418,8 @@
       <c r="AX264" s="1"/>
       <c r="AY264" s="1"/>
       <c r="AZ264" s="1"/>
-      <c r="BA264" s="1"/>
-    </row>
-    <row r="265" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -20736,9 +20472,8 @@
       <c r="AX265" s="1"/>
       <c r="AY265" s="1"/>
       <c r="AZ265" s="1"/>
-      <c r="BA265" s="1"/>
-    </row>
-    <row r="266" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -20791,9 +20526,8 @@
       <c r="AX266" s="1"/>
       <c r="AY266" s="1"/>
       <c r="AZ266" s="1"/>
-      <c r="BA266" s="1"/>
-    </row>
-    <row r="267" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -20846,9 +20580,8 @@
       <c r="AX267" s="1"/>
       <c r="AY267" s="1"/>
       <c r="AZ267" s="1"/>
-      <c r="BA267" s="1"/>
-    </row>
-    <row r="268" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -20901,9 +20634,8 @@
       <c r="AX268" s="1"/>
       <c r="AY268" s="1"/>
       <c r="AZ268" s="1"/>
-      <c r="BA268" s="1"/>
-    </row>
-    <row r="269" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -20956,9 +20688,8 @@
       <c r="AX269" s="1"/>
       <c r="AY269" s="1"/>
       <c r="AZ269" s="1"/>
-      <c r="BA269" s="1"/>
-    </row>
-    <row r="270" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -21011,9 +20742,8 @@
       <c r="AX270" s="1"/>
       <c r="AY270" s="1"/>
       <c r="AZ270" s="1"/>
-      <c r="BA270" s="1"/>
-    </row>
-    <row r="271" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -21066,9 +20796,8 @@
       <c r="AX271" s="1"/>
       <c r="AY271" s="1"/>
       <c r="AZ271" s="1"/>
-      <c r="BA271" s="1"/>
-    </row>
-    <row r="272" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -21121,9 +20850,8 @@
       <c r="AX272" s="1"/>
       <c r="AY272" s="1"/>
       <c r="AZ272" s="1"/>
-      <c r="BA272" s="1"/>
-    </row>
-    <row r="273" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -21176,9 +20904,8 @@
       <c r="AX273" s="1"/>
       <c r="AY273" s="1"/>
       <c r="AZ273" s="1"/>
-      <c r="BA273" s="1"/>
-    </row>
-    <row r="274" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -21231,9 +20958,8 @@
       <c r="AX274" s="1"/>
       <c r="AY274" s="1"/>
       <c r="AZ274" s="1"/>
-      <c r="BA274" s="1"/>
-    </row>
-    <row r="275" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -21286,9 +21012,8 @@
       <c r="AX275" s="1"/>
       <c r="AY275" s="1"/>
       <c r="AZ275" s="1"/>
-      <c r="BA275" s="1"/>
-    </row>
-    <row r="276" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -21341,9 +21066,8 @@
       <c r="AX276" s="1"/>
       <c r="AY276" s="1"/>
       <c r="AZ276" s="1"/>
-      <c r="BA276" s="1"/>
-    </row>
-    <row r="277" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -21396,9 +21120,8 @@
       <c r="AX277" s="1"/>
       <c r="AY277" s="1"/>
       <c r="AZ277" s="1"/>
-      <c r="BA277" s="1"/>
-    </row>
-    <row r="278" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -21451,9 +21174,8 @@
       <c r="AX278" s="1"/>
       <c r="AY278" s="1"/>
       <c r="AZ278" s="1"/>
-      <c r="BA278" s="1"/>
-    </row>
-    <row r="279" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -21506,9 +21228,8 @@
       <c r="AX279" s="1"/>
       <c r="AY279" s="1"/>
       <c r="AZ279" s="1"/>
-      <c r="BA279" s="1"/>
-    </row>
-    <row r="280" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -21561,9 +21282,8 @@
       <c r="AX280" s="1"/>
       <c r="AY280" s="1"/>
       <c r="AZ280" s="1"/>
-      <c r="BA280" s="1"/>
-    </row>
-    <row r="281" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -21616,9 +21336,8 @@
       <c r="AX281" s="1"/>
       <c r="AY281" s="1"/>
       <c r="AZ281" s="1"/>
-      <c r="BA281" s="1"/>
-    </row>
-    <row r="282" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -21671,9 +21390,8 @@
       <c r="AX282" s="1"/>
       <c r="AY282" s="1"/>
       <c r="AZ282" s="1"/>
-      <c r="BA282" s="1"/>
-    </row>
-    <row r="283" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -21726,9 +21444,8 @@
       <c r="AX283" s="1"/>
       <c r="AY283" s="1"/>
       <c r="AZ283" s="1"/>
-      <c r="BA283" s="1"/>
-    </row>
-    <row r="284" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -21781,9 +21498,8 @@
       <c r="AX284" s="1"/>
       <c r="AY284" s="1"/>
       <c r="AZ284" s="1"/>
-      <c r="BA284" s="1"/>
-    </row>
-    <row r="285" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -21836,9 +21552,8 @@
       <c r="AX285" s="1"/>
       <c r="AY285" s="1"/>
       <c r="AZ285" s="1"/>
-      <c r="BA285" s="1"/>
-    </row>
-    <row r="286" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -21891,9 +21606,8 @@
       <c r="AX286" s="1"/>
       <c r="AY286" s="1"/>
       <c r="AZ286" s="1"/>
-      <c r="BA286" s="1"/>
-    </row>
-    <row r="287" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -21946,9 +21660,8 @@
       <c r="AX287" s="1"/>
       <c r="AY287" s="1"/>
       <c r="AZ287" s="1"/>
-      <c r="BA287" s="1"/>
-    </row>
-    <row r="288" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -22001,9 +21714,8 @@
       <c r="AX288" s="1"/>
       <c r="AY288" s="1"/>
       <c r="AZ288" s="1"/>
-      <c r="BA288" s="1"/>
-    </row>
-    <row r="289" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -22056,9 +21768,8 @@
       <c r="AX289" s="1"/>
       <c r="AY289" s="1"/>
       <c r="AZ289" s="1"/>
-      <c r="BA289" s="1"/>
-    </row>
-    <row r="290" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -22111,9 +21822,8 @@
       <c r="AX290" s="1"/>
       <c r="AY290" s="1"/>
       <c r="AZ290" s="1"/>
-      <c r="BA290" s="1"/>
-    </row>
-    <row r="291" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -22166,9 +21876,8 @@
       <c r="AX291" s="1"/>
       <c r="AY291" s="1"/>
       <c r="AZ291" s="1"/>
-      <c r="BA291" s="1"/>
-    </row>
-    <row r="292" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -22221,9 +21930,8 @@
       <c r="AX292" s="1"/>
       <c r="AY292" s="1"/>
       <c r="AZ292" s="1"/>
-      <c r="BA292" s="1"/>
-    </row>
-    <row r="293" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -22276,9 +21984,8 @@
       <c r="AX293" s="1"/>
       <c r="AY293" s="1"/>
       <c r="AZ293" s="1"/>
-      <c r="BA293" s="1"/>
-    </row>
-    <row r="294" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -22331,9 +22038,8 @@
       <c r="AX294" s="1"/>
       <c r="AY294" s="1"/>
       <c r="AZ294" s="1"/>
-      <c r="BA294" s="1"/>
-    </row>
-    <row r="295" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -22386,9 +22092,8 @@
       <c r="AX295" s="1"/>
       <c r="AY295" s="1"/>
       <c r="AZ295" s="1"/>
-      <c r="BA295" s="1"/>
-    </row>
-    <row r="296" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -22441,9 +22146,8 @@
       <c r="AX296" s="1"/>
       <c r="AY296" s="1"/>
       <c r="AZ296" s="1"/>
-      <c r="BA296" s="1"/>
-    </row>
-    <row r="297" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -22496,9 +22200,8 @@
       <c r="AX297" s="1"/>
       <c r="AY297" s="1"/>
       <c r="AZ297" s="1"/>
-      <c r="BA297" s="1"/>
-    </row>
-    <row r="298" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -22551,9 +22254,8 @@
       <c r="AX298" s="1"/>
       <c r="AY298" s="1"/>
       <c r="AZ298" s="1"/>
-      <c r="BA298" s="1"/>
-    </row>
-    <row r="299" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -22606,9 +22308,8 @@
       <c r="AX299" s="1"/>
       <c r="AY299" s="1"/>
       <c r="AZ299" s="1"/>
-      <c r="BA299" s="1"/>
-    </row>
-    <row r="300" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -22661,9 +22362,8 @@
       <c r="AX300" s="1"/>
       <c r="AY300" s="1"/>
       <c r="AZ300" s="1"/>
-      <c r="BA300" s="1"/>
-    </row>
-    <row r="301" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -22716,9 +22416,8 @@
       <c r="AX301" s="1"/>
       <c r="AY301" s="1"/>
       <c r="AZ301" s="1"/>
-      <c r="BA301" s="1"/>
-    </row>
-    <row r="302" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -22771,9 +22470,8 @@
       <c r="AX302" s="1"/>
       <c r="AY302" s="1"/>
       <c r="AZ302" s="1"/>
-      <c r="BA302" s="1"/>
-    </row>
-    <row r="303" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -22826,9 +22524,8 @@
       <c r="AX303" s="1"/>
       <c r="AY303" s="1"/>
       <c r="AZ303" s="1"/>
-      <c r="BA303" s="1"/>
-    </row>
-    <row r="304" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="304" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -22881,9 +22578,8 @@
       <c r="AX304" s="1"/>
       <c r="AY304" s="1"/>
       <c r="AZ304" s="1"/>
-      <c r="BA304" s="1"/>
-    </row>
-    <row r="305" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="305" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -22936,9 +22632,8 @@
       <c r="AX305" s="1"/>
       <c r="AY305" s="1"/>
       <c r="AZ305" s="1"/>
-      <c r="BA305" s="1"/>
-    </row>
-    <row r="306" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="306" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -22991,9 +22686,8 @@
       <c r="AX306" s="1"/>
       <c r="AY306" s="1"/>
       <c r="AZ306" s="1"/>
-      <c r="BA306" s="1"/>
-    </row>
-    <row r="307" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="307" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -23046,9 +22740,8 @@
       <c r="AX307" s="1"/>
       <c r="AY307" s="1"/>
       <c r="AZ307" s="1"/>
-      <c r="BA307" s="1"/>
-    </row>
-    <row r="308" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="308" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -23101,9 +22794,8 @@
       <c r="AX308" s="1"/>
       <c r="AY308" s="1"/>
       <c r="AZ308" s="1"/>
-      <c r="BA308" s="1"/>
-    </row>
-    <row r="309" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -23156,9 +22848,8 @@
       <c r="AX309" s="1"/>
       <c r="AY309" s="1"/>
       <c r="AZ309" s="1"/>
-      <c r="BA309" s="1"/>
-    </row>
-    <row r="310" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="310" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -23211,9 +22902,8 @@
       <c r="AX310" s="1"/>
       <c r="AY310" s="1"/>
       <c r="AZ310" s="1"/>
-      <c r="BA310" s="1"/>
-    </row>
-    <row r="311" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="311" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -23266,9 +22956,8 @@
       <c r="AX311" s="1"/>
       <c r="AY311" s="1"/>
       <c r="AZ311" s="1"/>
-      <c r="BA311" s="1"/>
-    </row>
-    <row r="312" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="312" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -23321,9 +23010,8 @@
       <c r="AX312" s="1"/>
       <c r="AY312" s="1"/>
       <c r="AZ312" s="1"/>
-      <c r="BA312" s="1"/>
-    </row>
-    <row r="313" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="313" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -23376,9 +23064,8 @@
       <c r="AX313" s="1"/>
       <c r="AY313" s="1"/>
       <c r="AZ313" s="1"/>
-      <c r="BA313" s="1"/>
-    </row>
-    <row r="314" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -23431,9 +23118,8 @@
       <c r="AX314" s="1"/>
       <c r="AY314" s="1"/>
       <c r="AZ314" s="1"/>
-      <c r="BA314" s="1"/>
-    </row>
-    <row r="315" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="315" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -23486,9 +23172,8 @@
       <c r="AX315" s="1"/>
       <c r="AY315" s="1"/>
       <c r="AZ315" s="1"/>
-      <c r="BA315" s="1"/>
-    </row>
-    <row r="316" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="316" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -23541,9 +23226,8 @@
       <c r="AX316" s="1"/>
       <c r="AY316" s="1"/>
       <c r="AZ316" s="1"/>
-      <c r="BA316" s="1"/>
-    </row>
-    <row r="317" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -23596,9 +23280,8 @@
       <c r="AX317" s="1"/>
       <c r="AY317" s="1"/>
       <c r="AZ317" s="1"/>
-      <c r="BA317" s="1"/>
-    </row>
-    <row r="318" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -23651,9 +23334,8 @@
       <c r="AX318" s="1"/>
       <c r="AY318" s="1"/>
       <c r="AZ318" s="1"/>
-      <c r="BA318" s="1"/>
-    </row>
-    <row r="319" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -23706,9 +23388,8 @@
       <c r="AX319" s="1"/>
       <c r="AY319" s="1"/>
       <c r="AZ319" s="1"/>
-      <c r="BA319" s="1"/>
-    </row>
-    <row r="320" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -23761,9 +23442,8 @@
       <c r="AX320" s="1"/>
       <c r="AY320" s="1"/>
       <c r="AZ320" s="1"/>
-      <c r="BA320" s="1"/>
-    </row>
-    <row r="321" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -23816,9 +23496,8 @@
       <c r="AX321" s="1"/>
       <c r="AY321" s="1"/>
       <c r="AZ321" s="1"/>
-      <c r="BA321" s="1"/>
-    </row>
-    <row r="322" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -23871,9 +23550,8 @@
       <c r="AX322" s="1"/>
       <c r="AY322" s="1"/>
       <c r="AZ322" s="1"/>
-      <c r="BA322" s="1"/>
-    </row>
-    <row r="323" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -23926,9 +23604,8 @@
       <c r="AX323" s="1"/>
       <c r="AY323" s="1"/>
       <c r="AZ323" s="1"/>
-      <c r="BA323" s="1"/>
-    </row>
-    <row r="324" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -23981,9 +23658,8 @@
       <c r="AX324" s="1"/>
       <c r="AY324" s="1"/>
       <c r="AZ324" s="1"/>
-      <c r="BA324" s="1"/>
-    </row>
-    <row r="325" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -24036,9 +23712,8 @@
       <c r="AX325" s="1"/>
       <c r="AY325" s="1"/>
       <c r="AZ325" s="1"/>
-      <c r="BA325" s="1"/>
-    </row>
-    <row r="326" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -24091,9 +23766,8 @@
       <c r="AX326" s="1"/>
       <c r="AY326" s="1"/>
       <c r="AZ326" s="1"/>
-      <c r="BA326" s="1"/>
-    </row>
-    <row r="327" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -24146,9 +23820,8 @@
       <c r="AX327" s="1"/>
       <c r="AY327" s="1"/>
       <c r="AZ327" s="1"/>
-      <c r="BA327" s="1"/>
-    </row>
-    <row r="328" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -24201,9 +23874,8 @@
       <c r="AX328" s="1"/>
       <c r="AY328" s="1"/>
       <c r="AZ328" s="1"/>
-      <c r="BA328" s="1"/>
-    </row>
-    <row r="329" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -24256,9 +23928,8 @@
       <c r="AX329" s="1"/>
       <c r="AY329" s="1"/>
       <c r="AZ329" s="1"/>
-      <c r="BA329" s="1"/>
-    </row>
-    <row r="330" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -24311,9 +23982,8 @@
       <c r="AX330" s="1"/>
       <c r="AY330" s="1"/>
       <c r="AZ330" s="1"/>
-      <c r="BA330" s="1"/>
-    </row>
-    <row r="331" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -24366,9 +24036,8 @@
       <c r="AX331" s="1"/>
       <c r="AY331" s="1"/>
       <c r="AZ331" s="1"/>
-      <c r="BA331" s="1"/>
-    </row>
-    <row r="332" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -24421,9 +24090,8 @@
       <c r="AX332" s="1"/>
       <c r="AY332" s="1"/>
       <c r="AZ332" s="1"/>
-      <c r="BA332" s="1"/>
-    </row>
-    <row r="333" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -24476,9 +24144,8 @@
       <c r="AX333" s="1"/>
       <c r="AY333" s="1"/>
       <c r="AZ333" s="1"/>
-      <c r="BA333" s="1"/>
-    </row>
-    <row r="334" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -24531,9 +24198,8 @@
       <c r="AX334" s="1"/>
       <c r="AY334" s="1"/>
       <c r="AZ334" s="1"/>
-      <c r="BA334" s="1"/>
-    </row>
-    <row r="335" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -24586,9 +24252,8 @@
       <c r="AX335" s="1"/>
       <c r="AY335" s="1"/>
       <c r="AZ335" s="1"/>
-      <c r="BA335" s="1"/>
-    </row>
-    <row r="336" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -24641,9 +24306,8 @@
       <c r="AX336" s="1"/>
       <c r="AY336" s="1"/>
       <c r="AZ336" s="1"/>
-      <c r="BA336" s="1"/>
-    </row>
-    <row r="337" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -24696,9 +24360,8 @@
       <c r="AX337" s="1"/>
       <c r="AY337" s="1"/>
       <c r="AZ337" s="1"/>
-      <c r="BA337" s="1"/>
-    </row>
-    <row r="338" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -24751,9 +24414,8 @@
       <c r="AX338" s="1"/>
       <c r="AY338" s="1"/>
       <c r="AZ338" s="1"/>
-      <c r="BA338" s="1"/>
-    </row>
-    <row r="339" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="339" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -24806,9 +24468,8 @@
       <c r="AX339" s="1"/>
       <c r="AY339" s="1"/>
       <c r="AZ339" s="1"/>
-      <c r="BA339" s="1"/>
-    </row>
-    <row r="340" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="340" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -24861,9 +24522,8 @@
       <c r="AX340" s="1"/>
       <c r="AY340" s="1"/>
       <c r="AZ340" s="1"/>
-      <c r="BA340" s="1"/>
-    </row>
-    <row r="341" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -24916,9 +24576,8 @@
       <c r="AX341" s="1"/>
       <c r="AY341" s="1"/>
       <c r="AZ341" s="1"/>
-      <c r="BA341" s="1"/>
-    </row>
-    <row r="342" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -24971,9 +24630,8 @@
       <c r="AX342" s="1"/>
       <c r="AY342" s="1"/>
       <c r="AZ342" s="1"/>
-      <c r="BA342" s="1"/>
-    </row>
-    <row r="343" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -25026,9 +24684,8 @@
       <c r="AX343" s="1"/>
       <c r="AY343" s="1"/>
       <c r="AZ343" s="1"/>
-      <c r="BA343" s="1"/>
-    </row>
-    <row r="344" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -25081,9 +24738,8 @@
       <c r="AX344" s="1"/>
       <c r="AY344" s="1"/>
       <c r="AZ344" s="1"/>
-      <c r="BA344" s="1"/>
-    </row>
-    <row r="345" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -25136,9 +24792,8 @@
       <c r="AX345" s="1"/>
       <c r="AY345" s="1"/>
       <c r="AZ345" s="1"/>
-      <c r="BA345" s="1"/>
-    </row>
-    <row r="346" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -25191,9 +24846,8 @@
       <c r="AX346" s="1"/>
       <c r="AY346" s="1"/>
       <c r="AZ346" s="1"/>
-      <c r="BA346" s="1"/>
-    </row>
-    <row r="347" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -25246,9 +24900,8 @@
       <c r="AX347" s="1"/>
       <c r="AY347" s="1"/>
       <c r="AZ347" s="1"/>
-      <c r="BA347" s="1"/>
-    </row>
-    <row r="348" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -25301,9 +24954,8 @@
       <c r="AX348" s="1"/>
       <c r="AY348" s="1"/>
       <c r="AZ348" s="1"/>
-      <c r="BA348" s="1"/>
-    </row>
-    <row r="349" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -25356,9 +25008,8 @@
       <c r="AX349" s="1"/>
       <c r="AY349" s="1"/>
       <c r="AZ349" s="1"/>
-      <c r="BA349" s="1"/>
-    </row>
-    <row r="350" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -25411,9 +25062,8 @@
       <c r="AX350" s="1"/>
       <c r="AY350" s="1"/>
       <c r="AZ350" s="1"/>
-      <c r="BA350" s="1"/>
-    </row>
-    <row r="351" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -25466,9 +25116,8 @@
       <c r="AX351" s="1"/>
       <c r="AY351" s="1"/>
       <c r="AZ351" s="1"/>
-      <c r="BA351" s="1"/>
-    </row>
-    <row r="352" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -25521,9 +25170,8 @@
       <c r="AX352" s="1"/>
       <c r="AY352" s="1"/>
       <c r="AZ352" s="1"/>
-      <c r="BA352" s="1"/>
-    </row>
-    <row r="353" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -25576,9 +25224,8 @@
       <c r="AX353" s="1"/>
       <c r="AY353" s="1"/>
       <c r="AZ353" s="1"/>
-      <c r="BA353" s="1"/>
-    </row>
-    <row r="354" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -25631,9 +25278,8 @@
       <c r="AX354" s="1"/>
       <c r="AY354" s="1"/>
       <c r="AZ354" s="1"/>
-      <c r="BA354" s="1"/>
-    </row>
-    <row r="355" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -25686,9 +25332,8 @@
       <c r="AX355" s="1"/>
       <c r="AY355" s="1"/>
       <c r="AZ355" s="1"/>
-      <c r="BA355" s="1"/>
-    </row>
-    <row r="356" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -25741,9 +25386,8 @@
       <c r="AX356" s="1"/>
       <c r="AY356" s="1"/>
       <c r="AZ356" s="1"/>
-      <c r="BA356" s="1"/>
-    </row>
-    <row r="357" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -25796,9 +25440,8 @@
       <c r="AX357" s="1"/>
       <c r="AY357" s="1"/>
       <c r="AZ357" s="1"/>
-      <c r="BA357" s="1"/>
-    </row>
-    <row r="358" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -25851,9 +25494,8 @@
       <c r="AX358" s="1"/>
       <c r="AY358" s="1"/>
       <c r="AZ358" s="1"/>
-      <c r="BA358" s="1"/>
-    </row>
-    <row r="359" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -25906,9 +25548,8 @@
       <c r="AX359" s="1"/>
       <c r="AY359" s="1"/>
       <c r="AZ359" s="1"/>
-      <c r="BA359" s="1"/>
-    </row>
-    <row r="360" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -25961,9 +25602,8 @@
       <c r="AX360" s="1"/>
       <c r="AY360" s="1"/>
       <c r="AZ360" s="1"/>
-      <c r="BA360" s="1"/>
-    </row>
-    <row r="361" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -26016,9 +25656,8 @@
       <c r="AX361" s="1"/>
       <c r="AY361" s="1"/>
       <c r="AZ361" s="1"/>
-      <c r="BA361" s="1"/>
-    </row>
-    <row r="362" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -26071,9 +25710,8 @@
       <c r="AX362" s="1"/>
       <c r="AY362" s="1"/>
       <c r="AZ362" s="1"/>
-      <c r="BA362" s="1"/>
-    </row>
-    <row r="363" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -26126,9 +25764,8 @@
       <c r="AX363" s="1"/>
       <c r="AY363" s="1"/>
       <c r="AZ363" s="1"/>
-      <c r="BA363" s="1"/>
-    </row>
-    <row r="364" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -26181,9 +25818,8 @@
       <c r="AX364" s="1"/>
       <c r="AY364" s="1"/>
       <c r="AZ364" s="1"/>
-      <c r="BA364" s="1"/>
-    </row>
-    <row r="365" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -26236,9 +25872,8 @@
       <c r="AX365" s="1"/>
       <c r="AY365" s="1"/>
       <c r="AZ365" s="1"/>
-      <c r="BA365" s="1"/>
-    </row>
-    <row r="366" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -26291,9 +25926,8 @@
       <c r="AX366" s="1"/>
       <c r="AY366" s="1"/>
       <c r="AZ366" s="1"/>
-      <c r="BA366" s="1"/>
-    </row>
-    <row r="367" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -26346,9 +25980,8 @@
       <c r="AX367" s="1"/>
       <c r="AY367" s="1"/>
       <c r="AZ367" s="1"/>
-      <c r="BA367" s="1"/>
-    </row>
-    <row r="368" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -26401,9 +26034,8 @@
       <c r="AX368" s="1"/>
       <c r="AY368" s="1"/>
       <c r="AZ368" s="1"/>
-      <c r="BA368" s="1"/>
-    </row>
-    <row r="369" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -26456,9 +26088,8 @@
       <c r="AX369" s="1"/>
       <c r="AY369" s="1"/>
       <c r="AZ369" s="1"/>
-      <c r="BA369" s="1"/>
-    </row>
-    <row r="370" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -26511,9 +26142,8 @@
       <c r="AX370" s="1"/>
       <c r="AY370" s="1"/>
       <c r="AZ370" s="1"/>
-      <c r="BA370" s="1"/>
-    </row>
-    <row r="371" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -26566,9 +26196,8 @@
       <c r="AX371" s="1"/>
       <c r="AY371" s="1"/>
       <c r="AZ371" s="1"/>
-      <c r="BA371" s="1"/>
-    </row>
-    <row r="372" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -26621,9 +26250,8 @@
       <c r="AX372" s="1"/>
       <c r="AY372" s="1"/>
       <c r="AZ372" s="1"/>
-      <c r="BA372" s="1"/>
-    </row>
-    <row r="373" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -26676,9 +26304,8 @@
       <c r="AX373" s="1"/>
       <c r="AY373" s="1"/>
       <c r="AZ373" s="1"/>
-      <c r="BA373" s="1"/>
-    </row>
-    <row r="374" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -26731,9 +26358,8 @@
       <c r="AX374" s="1"/>
       <c r="AY374" s="1"/>
       <c r="AZ374" s="1"/>
-      <c r="BA374" s="1"/>
-    </row>
-    <row r="375" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -26786,9 +26412,8 @@
       <c r="AX375" s="1"/>
       <c r="AY375" s="1"/>
       <c r="AZ375" s="1"/>
-      <c r="BA375" s="1"/>
-    </row>
-    <row r="376" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -26841,9 +26466,8 @@
       <c r="AX376" s="1"/>
       <c r="AY376" s="1"/>
       <c r="AZ376" s="1"/>
-      <c r="BA376" s="1"/>
-    </row>
-    <row r="377" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -26896,9 +26520,8 @@
       <c r="AX377" s="1"/>
       <c r="AY377" s="1"/>
       <c r="AZ377" s="1"/>
-      <c r="BA377" s="1"/>
-    </row>
-    <row r="378" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -26951,9 +26574,8 @@
       <c r="AX378" s="1"/>
       <c r="AY378" s="1"/>
       <c r="AZ378" s="1"/>
-      <c r="BA378" s="1"/>
-    </row>
-    <row r="379" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -27006,9 +26628,8 @@
       <c r="AX379" s="1"/>
       <c r="AY379" s="1"/>
       <c r="AZ379" s="1"/>
-      <c r="BA379" s="1"/>
-    </row>
-    <row r="380" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -27061,9 +26682,8 @@
       <c r="AX380" s="1"/>
       <c r="AY380" s="1"/>
       <c r="AZ380" s="1"/>
-      <c r="BA380" s="1"/>
-    </row>
-    <row r="381" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -27116,9 +26736,8 @@
       <c r="AX381" s="1"/>
       <c r="AY381" s="1"/>
       <c r="AZ381" s="1"/>
-      <c r="BA381" s="1"/>
-    </row>
-    <row r="382" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -27171,9 +26790,8 @@
       <c r="AX382" s="1"/>
       <c r="AY382" s="1"/>
       <c r="AZ382" s="1"/>
-      <c r="BA382" s="1"/>
-    </row>
-    <row r="383" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -27226,9 +26844,8 @@
       <c r="AX383" s="1"/>
       <c r="AY383" s="1"/>
       <c r="AZ383" s="1"/>
-      <c r="BA383" s="1"/>
-    </row>
-    <row r="384" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -27281,9 +26898,8 @@
       <c r="AX384" s="1"/>
       <c r="AY384" s="1"/>
       <c r="AZ384" s="1"/>
-      <c r="BA384" s="1"/>
-    </row>
-    <row r="385" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -27336,9 +26952,8 @@
       <c r="AX385" s="1"/>
       <c r="AY385" s="1"/>
       <c r="AZ385" s="1"/>
-      <c r="BA385" s="1"/>
-    </row>
-    <row r="386" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -27391,9 +27006,8 @@
       <c r="AX386" s="1"/>
       <c r="AY386" s="1"/>
       <c r="AZ386" s="1"/>
-      <c r="BA386" s="1"/>
-    </row>
-    <row r="387" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -27446,9 +27060,8 @@
       <c r="AX387" s="1"/>
       <c r="AY387" s="1"/>
       <c r="AZ387" s="1"/>
-      <c r="BA387" s="1"/>
-    </row>
-    <row r="388" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -27501,9 +27114,8 @@
       <c r="AX388" s="1"/>
       <c r="AY388" s="1"/>
       <c r="AZ388" s="1"/>
-      <c r="BA388" s="1"/>
-    </row>
-    <row r="389" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -27556,9 +27168,8 @@
       <c r="AX389" s="1"/>
       <c r="AY389" s="1"/>
       <c r="AZ389" s="1"/>
-      <c r="BA389" s="1"/>
-    </row>
-    <row r="390" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -27611,9 +27222,8 @@
       <c r="AX390" s="1"/>
       <c r="AY390" s="1"/>
       <c r="AZ390" s="1"/>
-      <c r="BA390" s="1"/>
-    </row>
-    <row r="391" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -27666,9 +27276,8 @@
       <c r="AX391" s="1"/>
       <c r="AY391" s="1"/>
       <c r="AZ391" s="1"/>
-      <c r="BA391" s="1"/>
-    </row>
-    <row r="392" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="392" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -27721,9 +27330,8 @@
       <c r="AX392" s="1"/>
       <c r="AY392" s="1"/>
       <c r="AZ392" s="1"/>
-      <c r="BA392" s="1"/>
-    </row>
-    <row r="393" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -27776,9 +27384,8 @@
       <c r="AX393" s="1"/>
       <c r="AY393" s="1"/>
       <c r="AZ393" s="1"/>
-      <c r="BA393" s="1"/>
-    </row>
-    <row r="394" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -27831,9 +27438,8 @@
       <c r="AX394" s="1"/>
       <c r="AY394" s="1"/>
       <c r="AZ394" s="1"/>
-      <c r="BA394" s="1"/>
-    </row>
-    <row r="395" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -27886,9 +27492,8 @@
       <c r="AX395" s="1"/>
       <c r="AY395" s="1"/>
       <c r="AZ395" s="1"/>
-      <c r="BA395" s="1"/>
-    </row>
-    <row r="396" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -27941,9 +27546,8 @@
       <c r="AX396" s="1"/>
       <c r="AY396" s="1"/>
       <c r="AZ396" s="1"/>
-      <c r="BA396" s="1"/>
-    </row>
-    <row r="397" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -27996,9 +27600,8 @@
       <c r="AX397" s="1"/>
       <c r="AY397" s="1"/>
       <c r="AZ397" s="1"/>
-      <c r="BA397" s="1"/>
-    </row>
-    <row r="398" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -28051,9 +27654,8 @@
       <c r="AX398" s="1"/>
       <c r="AY398" s="1"/>
       <c r="AZ398" s="1"/>
-      <c r="BA398" s="1"/>
-    </row>
-    <row r="399" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -28106,9 +27708,8 @@
       <c r="AX399" s="1"/>
       <c r="AY399" s="1"/>
       <c r="AZ399" s="1"/>
-      <c r="BA399" s="1"/>
-    </row>
-    <row r="400" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="400" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -28161,9 +27762,8 @@
       <c r="AX400" s="1"/>
       <c r="AY400" s="1"/>
       <c r="AZ400" s="1"/>
-      <c r="BA400" s="1"/>
-    </row>
-    <row r="401" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="401" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -28216,9 +27816,8 @@
       <c r="AX401" s="1"/>
       <c r="AY401" s="1"/>
       <c r="AZ401" s="1"/>
-      <c r="BA401" s="1"/>
-    </row>
-    <row r="402" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="402" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -28271,9 +27870,8 @@
       <c r="AX402" s="1"/>
       <c r="AY402" s="1"/>
       <c r="AZ402" s="1"/>
-      <c r="BA402" s="1"/>
-    </row>
-    <row r="403" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="403" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -28326,9 +27924,8 @@
       <c r="AX403" s="1"/>
       <c r="AY403" s="1"/>
       <c r="AZ403" s="1"/>
-      <c r="BA403" s="1"/>
-    </row>
-    <row r="404" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="404" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -28381,9 +27978,8 @@
       <c r="AX404" s="1"/>
       <c r="AY404" s="1"/>
       <c r="AZ404" s="1"/>
-      <c r="BA404" s="1"/>
-    </row>
-    <row r="405" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="405" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -28436,9 +28032,8 @@
       <c r="AX405" s="1"/>
       <c r="AY405" s="1"/>
       <c r="AZ405" s="1"/>
-      <c r="BA405" s="1"/>
-    </row>
-    <row r="406" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -28491,9 +28086,8 @@
       <c r="AX406" s="1"/>
       <c r="AY406" s="1"/>
       <c r="AZ406" s="1"/>
-      <c r="BA406" s="1"/>
-    </row>
-    <row r="407" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="407" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -28546,9 +28140,8 @@
       <c r="AX407" s="1"/>
       <c r="AY407" s="1"/>
       <c r="AZ407" s="1"/>
-      <c r="BA407" s="1"/>
-    </row>
-    <row r="408" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="408" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -28601,9 +28194,8 @@
       <c r="AX408" s="1"/>
       <c r="AY408" s="1"/>
       <c r="AZ408" s="1"/>
-      <c r="BA408" s="1"/>
-    </row>
-    <row r="409" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="409" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -28656,9 +28248,8 @@
       <c r="AX409" s="1"/>
       <c r="AY409" s="1"/>
       <c r="AZ409" s="1"/>
-      <c r="BA409" s="1"/>
-    </row>
-    <row r="410" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="410" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -28711,9 +28302,8 @@
       <c r="AX410" s="1"/>
       <c r="AY410" s="1"/>
       <c r="AZ410" s="1"/>
-      <c r="BA410" s="1"/>
-    </row>
-    <row r="411" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="411" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -28766,9 +28356,8 @@
       <c r="AX411" s="1"/>
       <c r="AY411" s="1"/>
       <c r="AZ411" s="1"/>
-      <c r="BA411" s="1"/>
-    </row>
-    <row r="412" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="412" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -28821,9 +28410,8 @@
       <c r="AX412" s="1"/>
       <c r="AY412" s="1"/>
       <c r="AZ412" s="1"/>
-      <c r="BA412" s="1"/>
-    </row>
-    <row r="413" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="413" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -28876,9 +28464,8 @@
       <c r="AX413" s="1"/>
       <c r="AY413" s="1"/>
       <c r="AZ413" s="1"/>
-      <c r="BA413" s="1"/>
-    </row>
-    <row r="414" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="414" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -28931,9 +28518,8 @@
       <c r="AX414" s="1"/>
       <c r="AY414" s="1"/>
       <c r="AZ414" s="1"/>
-      <c r="BA414" s="1"/>
-    </row>
-    <row r="415" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="415" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -28986,9 +28572,8 @@
       <c r="AX415" s="1"/>
       <c r="AY415" s="1"/>
       <c r="AZ415" s="1"/>
-      <c r="BA415" s="1"/>
-    </row>
-    <row r="416" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="416" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -29041,9 +28626,8 @@
       <c r="AX416" s="1"/>
       <c r="AY416" s="1"/>
       <c r="AZ416" s="1"/>
-      <c r="BA416" s="1"/>
-    </row>
-    <row r="417" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="417" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -29096,9 +28680,8 @@
       <c r="AX417" s="1"/>
       <c r="AY417" s="1"/>
       <c r="AZ417" s="1"/>
-      <c r="BA417" s="1"/>
-    </row>
-    <row r="418" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="418" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -29151,9 +28734,8 @@
       <c r="AX418" s="1"/>
       <c r="AY418" s="1"/>
       <c r="AZ418" s="1"/>
-      <c r="BA418" s="1"/>
-    </row>
-    <row r="419" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="419" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -29206,9 +28788,8 @@
       <c r="AX419" s="1"/>
       <c r="AY419" s="1"/>
       <c r="AZ419" s="1"/>
-      <c r="BA419" s="1"/>
-    </row>
-    <row r="420" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="420" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -29261,9 +28842,8 @@
       <c r="AX420" s="1"/>
       <c r="AY420" s="1"/>
       <c r="AZ420" s="1"/>
-      <c r="BA420" s="1"/>
-    </row>
-    <row r="421" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="421" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -29316,9 +28896,8 @@
       <c r="AX421" s="1"/>
       <c r="AY421" s="1"/>
       <c r="AZ421" s="1"/>
-      <c r="BA421" s="1"/>
-    </row>
-    <row r="422" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="422" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -29371,9 +28950,8 @@
       <c r="AX422" s="1"/>
       <c r="AY422" s="1"/>
       <c r="AZ422" s="1"/>
-      <c r="BA422" s="1"/>
-    </row>
-    <row r="423" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -29426,9 +29004,8 @@
       <c r="AX423" s="1"/>
       <c r="AY423" s="1"/>
       <c r="AZ423" s="1"/>
-      <c r="BA423" s="1"/>
-    </row>
-    <row r="424" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -29481,9 +29058,8 @@
       <c r="AX424" s="1"/>
       <c r="AY424" s="1"/>
       <c r="AZ424" s="1"/>
-      <c r="BA424" s="1"/>
-    </row>
-    <row r="425" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="425" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -29536,9 +29112,8 @@
       <c r="AX425" s="1"/>
       <c r="AY425" s="1"/>
       <c r="AZ425" s="1"/>
-      <c r="BA425" s="1"/>
-    </row>
-    <row r="426" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="426" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -29591,9 +29166,8 @@
       <c r="AX426" s="1"/>
       <c r="AY426" s="1"/>
       <c r="AZ426" s="1"/>
-      <c r="BA426" s="1"/>
-    </row>
-    <row r="427" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="427" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -29646,9 +29220,8 @@
       <c r="AX427" s="1"/>
       <c r="AY427" s="1"/>
       <c r="AZ427" s="1"/>
-      <c r="BA427" s="1"/>
-    </row>
-    <row r="428" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="428" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -29701,9 +29274,8 @@
       <c r="AX428" s="1"/>
       <c r="AY428" s="1"/>
       <c r="AZ428" s="1"/>
-      <c r="BA428" s="1"/>
-    </row>
-    <row r="429" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="429" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -29756,9 +29328,8 @@
       <c r="AX429" s="1"/>
       <c r="AY429" s="1"/>
       <c r="AZ429" s="1"/>
-      <c r="BA429" s="1"/>
-    </row>
-    <row r="430" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="430" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -29811,9 +29382,8 @@
       <c r="AX430" s="1"/>
       <c r="AY430" s="1"/>
       <c r="AZ430" s="1"/>
-      <c r="BA430" s="1"/>
-    </row>
-    <row r="431" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="431" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -29866,9 +29436,8 @@
       <c r="AX431" s="1"/>
       <c r="AY431" s="1"/>
       <c r="AZ431" s="1"/>
-      <c r="BA431" s="1"/>
-    </row>
-    <row r="432" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="432" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -29921,9 +29490,8 @@
       <c r="AX432" s="1"/>
       <c r="AY432" s="1"/>
       <c r="AZ432" s="1"/>
-      <c r="BA432" s="1"/>
-    </row>
-    <row r="433" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -29976,9 +29544,8 @@
       <c r="AX433" s="1"/>
       <c r="AY433" s="1"/>
       <c r="AZ433" s="1"/>
-      <c r="BA433" s="1"/>
-    </row>
-    <row r="434" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -30031,9 +29598,8 @@
       <c r="AX434" s="1"/>
       <c r="AY434" s="1"/>
       <c r="AZ434" s="1"/>
-      <c r="BA434" s="1"/>
-    </row>
-    <row r="435" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="435" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -30086,9 +29652,8 @@
       <c r="AX435" s="1"/>
       <c r="AY435" s="1"/>
       <c r="AZ435" s="1"/>
-      <c r="BA435" s="1"/>
-    </row>
-    <row r="436" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="436" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -30141,9 +29706,8 @@
       <c r="AX436" s="1"/>
       <c r="AY436" s="1"/>
       <c r="AZ436" s="1"/>
-      <c r="BA436" s="1"/>
-    </row>
-    <row r="437" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="437" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -30196,9 +29760,8 @@
       <c r="AX437" s="1"/>
       <c r="AY437" s="1"/>
       <c r="AZ437" s="1"/>
-      <c r="BA437" s="1"/>
-    </row>
-    <row r="438" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="438" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -30251,9 +29814,8 @@
       <c r="AX438" s="1"/>
       <c r="AY438" s="1"/>
       <c r="AZ438" s="1"/>
-      <c r="BA438" s="1"/>
-    </row>
-    <row r="439" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="439" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -30306,9 +29868,8 @@
       <c r="AX439" s="1"/>
       <c r="AY439" s="1"/>
       <c r="AZ439" s="1"/>
-      <c r="BA439" s="1"/>
-    </row>
-    <row r="440" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="440" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -30361,9 +29922,8 @@
       <c r="AX440" s="1"/>
       <c r="AY440" s="1"/>
       <c r="AZ440" s="1"/>
-      <c r="BA440" s="1"/>
-    </row>
-    <row r="441" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="441" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -30416,9 +29976,8 @@
       <c r="AX441" s="1"/>
       <c r="AY441" s="1"/>
       <c r="AZ441" s="1"/>
-      <c r="BA441" s="1"/>
-    </row>
-    <row r="442" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="442" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -30471,9 +30030,8 @@
       <c r="AX442" s="1"/>
       <c r="AY442" s="1"/>
       <c r="AZ442" s="1"/>
-      <c r="BA442" s="1"/>
-    </row>
-    <row r="443" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="443" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -30526,9 +30084,8 @@
       <c r="AX443" s="1"/>
       <c r="AY443" s="1"/>
       <c r="AZ443" s="1"/>
-      <c r="BA443" s="1"/>
-    </row>
-    <row r="444" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="444" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -30581,9 +30138,8 @@
       <c r="AX444" s="1"/>
       <c r="AY444" s="1"/>
       <c r="AZ444" s="1"/>
-      <c r="BA444" s="1"/>
-    </row>
-    <row r="445" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="445" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -30636,9 +30192,8 @@
       <c r="AX445" s="1"/>
       <c r="AY445" s="1"/>
       <c r="AZ445" s="1"/>
-      <c r="BA445" s="1"/>
-    </row>
-    <row r="446" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="446" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -30691,9 +30246,8 @@
       <c r="AX446" s="1"/>
       <c r="AY446" s="1"/>
       <c r="AZ446" s="1"/>
-      <c r="BA446" s="1"/>
-    </row>
-    <row r="447" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="447" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -30746,9 +30300,8 @@
       <c r="AX447" s="1"/>
       <c r="AY447" s="1"/>
       <c r="AZ447" s="1"/>
-      <c r="BA447" s="1"/>
-    </row>
-    <row r="448" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -30801,9 +30354,8 @@
       <c r="AX448" s="1"/>
       <c r="AY448" s="1"/>
       <c r="AZ448" s="1"/>
-      <c r="BA448" s="1"/>
-    </row>
-    <row r="449" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -30856,9 +30408,8 @@
       <c r="AX449" s="1"/>
       <c r="AY449" s="1"/>
       <c r="AZ449" s="1"/>
-      <c r="BA449" s="1"/>
-    </row>
-    <row r="450" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="450" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -30911,9 +30462,8 @@
       <c r="AX450" s="1"/>
       <c r="AY450" s="1"/>
       <c r="AZ450" s="1"/>
-      <c r="BA450" s="1"/>
-    </row>
-    <row r="451" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="451" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -30966,9 +30516,8 @@
       <c r="AX451" s="1"/>
       <c r="AY451" s="1"/>
       <c r="AZ451" s="1"/>
-      <c r="BA451" s="1"/>
-    </row>
-    <row r="452" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="452" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -31021,9 +30570,8 @@
       <c r="AX452" s="1"/>
       <c r="AY452" s="1"/>
       <c r="AZ452" s="1"/>
-      <c r="BA452" s="1"/>
-    </row>
-    <row r="453" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="453" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -31076,9 +30624,8 @@
       <c r="AX453" s="1"/>
       <c r="AY453" s="1"/>
       <c r="AZ453" s="1"/>
-      <c r="BA453" s="1"/>
-    </row>
-    <row r="454" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="454" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -31131,9 +30678,8 @@
       <c r="AX454" s="1"/>
       <c r="AY454" s="1"/>
       <c r="AZ454" s="1"/>
-      <c r="BA454" s="1"/>
-    </row>
-    <row r="455" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="455" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -31186,9 +30732,8 @@
       <c r="AX455" s="1"/>
       <c r="AY455" s="1"/>
       <c r="AZ455" s="1"/>
-      <c r="BA455" s="1"/>
-    </row>
-    <row r="456" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="456" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -31241,9 +30786,8 @@
       <c r="AX456" s="1"/>
       <c r="AY456" s="1"/>
       <c r="AZ456" s="1"/>
-      <c r="BA456" s="1"/>
-    </row>
-    <row r="457" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="457" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -31296,9 +30840,8 @@
       <c r="AX457" s="1"/>
       <c r="AY457" s="1"/>
       <c r="AZ457" s="1"/>
-      <c r="BA457" s="1"/>
-    </row>
-    <row r="458" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="458" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -31351,9 +30894,8 @@
       <c r="AX458" s="1"/>
       <c r="AY458" s="1"/>
       <c r="AZ458" s="1"/>
-      <c r="BA458" s="1"/>
-    </row>
-    <row r="459" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="459" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -31406,9 +30948,8 @@
       <c r="AX459" s="1"/>
       <c r="AY459" s="1"/>
       <c r="AZ459" s="1"/>
-      <c r="BA459" s="1"/>
-    </row>
-    <row r="460" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="460" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -31461,9 +31002,8 @@
       <c r="AX460" s="1"/>
       <c r="AY460" s="1"/>
       <c r="AZ460" s="1"/>
-      <c r="BA460" s="1"/>
-    </row>
-    <row r="461" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="461" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -31516,9 +31056,8 @@
       <c r="AX461" s="1"/>
       <c r="AY461" s="1"/>
       <c r="AZ461" s="1"/>
-      <c r="BA461" s="1"/>
-    </row>
-    <row r="462" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="462" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -31571,9 +31110,8 @@
       <c r="AX462" s="1"/>
       <c r="AY462" s="1"/>
       <c r="AZ462" s="1"/>
-      <c r="BA462" s="1"/>
-    </row>
-    <row r="463" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="463" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -31626,9 +31164,8 @@
       <c r="AX463" s="1"/>
       <c r="AY463" s="1"/>
       <c r="AZ463" s="1"/>
-      <c r="BA463" s="1"/>
-    </row>
-    <row r="464" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="464" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -31681,9 +31218,8 @@
       <c r="AX464" s="1"/>
       <c r="AY464" s="1"/>
       <c r="AZ464" s="1"/>
-      <c r="BA464" s="1"/>
-    </row>
-    <row r="465" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="465" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -31736,9 +31272,8 @@
       <c r="AX465" s="1"/>
       <c r="AY465" s="1"/>
       <c r="AZ465" s="1"/>
-      <c r="BA465" s="1"/>
-    </row>
-    <row r="466" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="466" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -31791,9 +31326,8 @@
       <c r="AX466" s="1"/>
       <c r="AY466" s="1"/>
       <c r="AZ466" s="1"/>
-      <c r="BA466" s="1"/>
-    </row>
-    <row r="467" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="467" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -31846,9 +31380,8 @@
       <c r="AX467" s="1"/>
       <c r="AY467" s="1"/>
       <c r="AZ467" s="1"/>
-      <c r="BA467" s="1"/>
-    </row>
-    <row r="468" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="468" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -31901,9 +31434,8 @@
       <c r="AX468" s="1"/>
       <c r="AY468" s="1"/>
       <c r="AZ468" s="1"/>
-      <c r="BA468" s="1"/>
-    </row>
-    <row r="469" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="469" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -31956,9 +31488,8 @@
       <c r="AX469" s="1"/>
       <c r="AY469" s="1"/>
       <c r="AZ469" s="1"/>
-      <c r="BA469" s="1"/>
-    </row>
-    <row r="470" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="470" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -32011,9 +31542,8 @@
       <c r="AX470" s="1"/>
       <c r="AY470" s="1"/>
       <c r="AZ470" s="1"/>
-      <c r="BA470" s="1"/>
-    </row>
-    <row r="471" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="471" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -32066,9 +31596,8 @@
       <c r="AX471" s="1"/>
       <c r="AY471" s="1"/>
       <c r="AZ471" s="1"/>
-      <c r="BA471" s="1"/>
-    </row>
-    <row r="472" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="472" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -32121,9 +31650,8 @@
       <c r="AX472" s="1"/>
       <c r="AY472" s="1"/>
       <c r="AZ472" s="1"/>
-      <c r="BA472" s="1"/>
-    </row>
-    <row r="473" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="473" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -32176,9 +31704,8 @@
       <c r="AX473" s="1"/>
       <c r="AY473" s="1"/>
       <c r="AZ473" s="1"/>
-      <c r="BA473" s="1"/>
-    </row>
-    <row r="474" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="474" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -32231,9 +31758,8 @@
       <c r="AX474" s="1"/>
       <c r="AY474" s="1"/>
       <c r="AZ474" s="1"/>
-      <c r="BA474" s="1"/>
-    </row>
-    <row r="475" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="475" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -32286,9 +31812,8 @@
       <c r="AX475" s="1"/>
       <c r="AY475" s="1"/>
       <c r="AZ475" s="1"/>
-      <c r="BA475" s="1"/>
-    </row>
-    <row r="476" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="476" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -32341,9 +31866,8 @@
       <c r="AX476" s="1"/>
       <c r="AY476" s="1"/>
       <c r="AZ476" s="1"/>
-      <c r="BA476" s="1"/>
-    </row>
-    <row r="477" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="477" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -32396,9 +31920,8 @@
       <c r="AX477" s="1"/>
       <c r="AY477" s="1"/>
       <c r="AZ477" s="1"/>
-      <c r="BA477" s="1"/>
-    </row>
-    <row r="478" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="478" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -32451,9 +31974,8 @@
       <c r="AX478" s="1"/>
       <c r="AY478" s="1"/>
       <c r="AZ478" s="1"/>
-      <c r="BA478" s="1"/>
-    </row>
-    <row r="479" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="479" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -32506,9 +32028,8 @@
       <c r="AX479" s="1"/>
       <c r="AY479" s="1"/>
       <c r="AZ479" s="1"/>
-      <c r="BA479" s="1"/>
-    </row>
-    <row r="480" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="480" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -32561,9 +32082,8 @@
       <c r="AX480" s="1"/>
       <c r="AY480" s="1"/>
       <c r="AZ480" s="1"/>
-      <c r="BA480" s="1"/>
-    </row>
-    <row r="481" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="481" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -32616,9 +32136,8 @@
       <c r="AX481" s="1"/>
       <c r="AY481" s="1"/>
       <c r="AZ481" s="1"/>
-      <c r="BA481" s="1"/>
-    </row>
-    <row r="482" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -32671,9 +32190,8 @@
       <c r="AX482" s="1"/>
       <c r="AY482" s="1"/>
       <c r="AZ482" s="1"/>
-      <c r="BA482" s="1"/>
-    </row>
-    <row r="483" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="483" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -32726,9 +32244,8 @@
       <c r="AX483" s="1"/>
       <c r="AY483" s="1"/>
       <c r="AZ483" s="1"/>
-      <c r="BA483" s="1"/>
-    </row>
-    <row r="484" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="484" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -32781,9 +32298,8 @@
       <c r="AX484" s="1"/>
       <c r="AY484" s="1"/>
       <c r="AZ484" s="1"/>
-      <c r="BA484" s="1"/>
-    </row>
-    <row r="485" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -32836,9 +32352,8 @@
       <c r="AX485" s="1"/>
       <c r="AY485" s="1"/>
       <c r="AZ485" s="1"/>
-      <c r="BA485" s="1"/>
-    </row>
-    <row r="486" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="486" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -32891,9 +32406,8 @@
       <c r="AX486" s="1"/>
       <c r="AY486" s="1"/>
       <c r="AZ486" s="1"/>
-      <c r="BA486" s="1"/>
-    </row>
-    <row r="487" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="487" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -32946,9 +32460,8 @@
       <c r="AX487" s="1"/>
       <c r="AY487" s="1"/>
       <c r="AZ487" s="1"/>
-      <c r="BA487" s="1"/>
-    </row>
-    <row r="488" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -33001,9 +32514,8 @@
       <c r="AX488" s="1"/>
       <c r="AY488" s="1"/>
       <c r="AZ488" s="1"/>
-      <c r="BA488" s="1"/>
-    </row>
-    <row r="489" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="489" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -33056,9 +32568,8 @@
       <c r="AX489" s="1"/>
       <c r="AY489" s="1"/>
       <c r="AZ489" s="1"/>
-      <c r="BA489" s="1"/>
-    </row>
-    <row r="490" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -33111,9 +32622,8 @@
       <c r="AX490" s="1"/>
       <c r="AY490" s="1"/>
       <c r="AZ490" s="1"/>
-      <c r="BA490" s="1"/>
-    </row>
-    <row r="491" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="491" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -33166,9 +32676,8 @@
       <c r="AX491" s="1"/>
       <c r="AY491" s="1"/>
       <c r="AZ491" s="1"/>
-      <c r="BA491" s="1"/>
-    </row>
-    <row r="492" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="492" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -33221,9 +32730,8 @@
       <c r="AX492" s="1"/>
       <c r="AY492" s="1"/>
       <c r="AZ492" s="1"/>
-      <c r="BA492" s="1"/>
-    </row>
-    <row r="493" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="493" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -33276,9 +32784,8 @@
       <c r="AX493" s="1"/>
       <c r="AY493" s="1"/>
       <c r="AZ493" s="1"/>
-      <c r="BA493" s="1"/>
-    </row>
-    <row r="494" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="494" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -33331,9 +32838,8 @@
       <c r="AX494" s="1"/>
       <c r="AY494" s="1"/>
       <c r="AZ494" s="1"/>
-      <c r="BA494" s="1"/>
-    </row>
-    <row r="495" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="495" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -33386,9 +32892,8 @@
       <c r="AX495" s="1"/>
       <c r="AY495" s="1"/>
       <c r="AZ495" s="1"/>
-      <c r="BA495" s="1"/>
-    </row>
-    <row r="496" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="496" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -33441,9 +32946,8 @@
       <c r="AX496" s="1"/>
       <c r="AY496" s="1"/>
       <c r="AZ496" s="1"/>
-      <c r="BA496" s="1"/>
-    </row>
-    <row r="497" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="497" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -33496,9 +33000,8 @@
       <c r="AX497" s="1"/>
       <c r="AY497" s="1"/>
       <c r="AZ497" s="1"/>
-      <c r="BA497" s="1"/>
-    </row>
-    <row r="498" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="498" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -33551,9 +33054,8 @@
       <c r="AX498" s="1"/>
       <c r="AY498" s="1"/>
       <c r="AZ498" s="1"/>
-      <c r="BA498" s="1"/>
-    </row>
-    <row r="499" spans="1:53" x14ac:dyDescent="0.25">
+    </row>
+    <row r="499" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -33606,7 +33108,6 @@
       <c r="AX499" s="1"/>
       <c r="AY499" s="1"/>
       <c r="AZ499" s="1"/>
-      <c r="BA499" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AD94" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
